--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90222</v>
+        <v>90232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>90222</v>
+        <v>90232</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90232</v>
+        <v>90244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B22" t="n">
-        <v>90232</v>
+        <v>91979</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R22" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B23" t="n">
-        <v>91967</v>
+        <v>90244</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R23" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3241,6 +3241,3576 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121495659</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100361</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>494954</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6992160</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121495695</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92019</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>495069</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991736</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121495704</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>495047</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991920</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121495709</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98012</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>495057</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991872</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121495682</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>495314</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991997</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121495710</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>494983</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991722</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121495713</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101264</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494943</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991755</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121495697</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101264</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>495040</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991930</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121495654</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100361</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>495089</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6992087</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121495724</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>495179</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6992005</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121495705</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92019</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>495117</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991892</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121495717</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100270</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>495355</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991976</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121495693</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>495317</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991944</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121495712</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100270</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>495313</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991949</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121495701</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101264</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>495371</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991950</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121495689</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90245</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>495313</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991964</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121495684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101264</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>495352</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991979</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121495683</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91978</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>495158</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991970</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121495634</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100361</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>495050</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6992120</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121495725</v>
+      </c>
+      <c r="B43" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>494962</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991783</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121495691</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91643</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>494951</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991725</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121495696</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91980</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>495158</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991970</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121495715</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90245</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>495040</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991932</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121495699</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90245</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>495037</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991941</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121495686</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92019</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>494949</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991727</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121495723</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92019</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>494964</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6991779</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121495722</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97108</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>495023</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991790</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121495726</v>
+      </c>
+      <c r="B51" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>494938</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6991772</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121495700</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92019</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>495333</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6991958</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121495702</v>
+      </c>
+      <c r="B53" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>495369</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6991950</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121495746</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90172</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>495314</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6991947</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121495688</v>
+      </c>
+      <c r="B55" t="n">
+        <v>100361</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>495370</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6991950</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121495706</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100361</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>495276</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6991998</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121495716</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92017</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>495158</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6991970</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121495694</v>
+      </c>
+      <c r="B58" t="n">
+        <v>103609</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>495054</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6991738</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90244</v>
+        <v>90245</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>91979</v>
+        <v>90245</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R22" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>90244</v>
+        <v>91980</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R23" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495659</v>
+        <v>121495723</v>
       </c>
       <c r="B24" t="n">
-        <v>100361</v>
+        <v>92019</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494954</v>
+        <v>494964</v>
       </c>
       <c r="R24" t="n">
-        <v>6992160</v>
+        <v>6991779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,7 +3346,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495695</v>
+        <v>121495705</v>
       </c>
       <c r="B25" t="n">
         <v>92019</v>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495069</v>
+        <v>495117</v>
       </c>
       <c r="R25" t="n">
-        <v>6991736</v>
+        <v>6991892</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495704</v>
+        <v>121495688</v>
       </c>
       <c r="B26" t="n">
-        <v>98095</v>
+        <v>100361</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495047</v>
+        <v>495370</v>
       </c>
       <c r="R26" t="n">
-        <v>6991920</v>
+        <v>6991950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495709</v>
+        <v>121495722</v>
       </c>
       <c r="B27" t="n">
-        <v>98012</v>
+        <v>97108</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495057</v>
+        <v>495023</v>
       </c>
       <c r="R27" t="n">
-        <v>6991872</v>
+        <v>6991790</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495682</v>
+        <v>121495683</v>
       </c>
       <c r="B28" t="n">
-        <v>103609</v>
+        <v>91978</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495314</v>
+        <v>495158</v>
       </c>
       <c r="R28" t="n">
-        <v>6991997</v>
+        <v>6991970</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495710</v>
+        <v>121495700</v>
       </c>
       <c r="B29" t="n">
-        <v>98095</v>
+        <v>92019</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,25 +3766,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494983</v>
+        <v>495333</v>
       </c>
       <c r="R29" t="n">
-        <v>6991722</v>
+        <v>6991958</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495713</v>
+        <v>121495634</v>
       </c>
       <c r="B30" t="n">
-        <v>101264</v>
+        <v>100361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494943</v>
+        <v>495050</v>
       </c>
       <c r="R30" t="n">
-        <v>6991755</v>
+        <v>6992120</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495697</v>
+        <v>121495702</v>
       </c>
       <c r="B31" t="n">
-        <v>101264</v>
+        <v>103609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495040</v>
+        <v>495369</v>
       </c>
       <c r="R31" t="n">
-        <v>6991930</v>
+        <v>6991950</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495654</v>
+        <v>121495710</v>
       </c>
       <c r="B32" t="n">
-        <v>100361</v>
+        <v>98095</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495089</v>
+        <v>494983</v>
       </c>
       <c r="R32" t="n">
-        <v>6992087</v>
+        <v>6991722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495724</v>
+        <v>121495701</v>
       </c>
       <c r="B33" t="n">
-        <v>98095</v>
+        <v>101264</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495179</v>
+        <v>495371</v>
       </c>
       <c r="R33" t="n">
-        <v>6992005</v>
+        <v>6991950</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495705</v>
+        <v>121495695</v>
       </c>
       <c r="B34" t="n">
         <v>92019</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495117</v>
+        <v>495069</v>
       </c>
       <c r="R34" t="n">
-        <v>6991892</v>
+        <v>6991736</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495717</v>
+        <v>121495712</v>
       </c>
       <c r="B35" t="n">
         <v>100270</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495355</v>
+        <v>495313</v>
       </c>
       <c r="R35" t="n">
-        <v>6991976</v>
+        <v>6991949</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495712</v>
+        <v>121495697</v>
       </c>
       <c r="B37" t="n">
-        <v>100270</v>
+        <v>101264</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495313</v>
+        <v>495040</v>
       </c>
       <c r="R37" t="n">
-        <v>6991949</v>
+        <v>6991930</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495701</v>
+        <v>121495715</v>
       </c>
       <c r="B38" t="n">
-        <v>101264</v>
+        <v>90245</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495371</v>
+        <v>495040</v>
       </c>
       <c r="R38" t="n">
-        <v>6991950</v>
+        <v>6991932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495689</v>
+        <v>121495694</v>
       </c>
       <c r="B39" t="n">
-        <v>90245</v>
+        <v>103609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495313</v>
+        <v>495054</v>
       </c>
       <c r="R39" t="n">
-        <v>6991964</v>
+        <v>6991738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495684</v>
+        <v>121495682</v>
       </c>
       <c r="B40" t="n">
-        <v>101264</v>
+        <v>103609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495352</v>
+        <v>495314</v>
       </c>
       <c r="R40" t="n">
-        <v>6991979</v>
+        <v>6991997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495683</v>
+        <v>121495713</v>
       </c>
       <c r="B41" t="n">
-        <v>91978</v>
+        <v>101264</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495158</v>
+        <v>494943</v>
       </c>
       <c r="R41" t="n">
-        <v>6991970</v>
+        <v>6991755</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495634</v>
+        <v>121495696</v>
       </c>
       <c r="B42" t="n">
-        <v>100361</v>
+        <v>91980</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495050</v>
+        <v>495158</v>
       </c>
       <c r="R42" t="n">
-        <v>6992120</v>
+        <v>6991970</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495725</v>
+        <v>121495691</v>
       </c>
       <c r="B43" t="n">
-        <v>103609</v>
+        <v>91643</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494962</v>
+        <v>494951</v>
       </c>
       <c r="R43" t="n">
-        <v>6991783</v>
+        <v>6991725</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495691</v>
+        <v>121495724</v>
       </c>
       <c r="B44" t="n">
-        <v>91643</v>
+        <v>98095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5296,25 +5296,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494951</v>
+        <v>495179</v>
       </c>
       <c r="R44" t="n">
-        <v>6991725</v>
+        <v>6992005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495696</v>
+        <v>121495709</v>
       </c>
       <c r="B45" t="n">
-        <v>91980</v>
+        <v>98012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495158</v>
+        <v>495057</v>
       </c>
       <c r="R45" t="n">
-        <v>6991970</v>
+        <v>6991872</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495715</v>
+        <v>121495746</v>
       </c>
       <c r="B46" t="n">
-        <v>90245</v>
+        <v>90172</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495040</v>
+        <v>495314</v>
       </c>
       <c r="R46" t="n">
-        <v>6991932</v>
+        <v>6991947</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495699</v>
+        <v>121495704</v>
       </c>
       <c r="B47" t="n">
-        <v>90245</v>
+        <v>98095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495037</v>
+        <v>495047</v>
       </c>
       <c r="R47" t="n">
-        <v>6991941</v>
+        <v>6991920</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495723</v>
+        <v>121495717</v>
       </c>
       <c r="B49" t="n">
-        <v>92019</v>
+        <v>100270</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494964</v>
+        <v>495355</v>
       </c>
       <c r="R49" t="n">
-        <v>6991779</v>
+        <v>6991976</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495722</v>
+        <v>121495706</v>
       </c>
       <c r="B50" t="n">
-        <v>97108</v>
+        <v>100361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221063</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495023</v>
+        <v>495276</v>
       </c>
       <c r="R50" t="n">
-        <v>6991790</v>
+        <v>6991998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495726</v>
+        <v>121495659</v>
       </c>
       <c r="B51" t="n">
-        <v>103609</v>
+        <v>100361</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494938</v>
+        <v>494954</v>
       </c>
       <c r="R51" t="n">
-        <v>6991772</v>
+        <v>6992160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495700</v>
+        <v>121495654</v>
       </c>
       <c r="B52" t="n">
-        <v>92019</v>
+        <v>100361</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495333</v>
+        <v>495089</v>
       </c>
       <c r="R52" t="n">
-        <v>6991958</v>
+        <v>6992087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495702</v>
+        <v>121495684</v>
       </c>
       <c r="B53" t="n">
-        <v>103609</v>
+        <v>101264</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495369</v>
+        <v>495352</v>
       </c>
       <c r="R53" t="n">
-        <v>6991950</v>
+        <v>6991979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495746</v>
+        <v>121495726</v>
       </c>
       <c r="B54" t="n">
-        <v>90172</v>
+        <v>103609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3286</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495314</v>
+        <v>494938</v>
       </c>
       <c r="R54" t="n">
-        <v>6991947</v>
+        <v>6991772</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495688</v>
+        <v>121495689</v>
       </c>
       <c r="B55" t="n">
-        <v>100361</v>
+        <v>90245</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495370</v>
+        <v>495313</v>
       </c>
       <c r="R55" t="n">
-        <v>6991950</v>
+        <v>6991964</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495706</v>
+        <v>121495725</v>
       </c>
       <c r="B56" t="n">
-        <v>100361</v>
+        <v>103609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495276</v>
+        <v>494962</v>
       </c>
       <c r="R56" t="n">
-        <v>6991998</v>
+        <v>6991783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495694</v>
+        <v>121495699</v>
       </c>
       <c r="B58" t="n">
-        <v>103609</v>
+        <v>90245</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,25 +6724,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495054</v>
+        <v>495037</v>
       </c>
       <c r="R58" t="n">
-        <v>6991738</v>
+        <v>6991941</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90245</v>
+        <v>90248</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B22" t="n">
-        <v>90245</v>
+        <v>91983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R22" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B23" t="n">
-        <v>91980</v>
+        <v>90248</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R23" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495723</v>
+        <v>121495724</v>
       </c>
       <c r="B24" t="n">
-        <v>92019</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494964</v>
+        <v>495179</v>
       </c>
       <c r="R24" t="n">
-        <v>6991779</v>
+        <v>6992005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495705</v>
+        <v>121495712</v>
       </c>
       <c r="B25" t="n">
-        <v>92019</v>
+        <v>100273</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495117</v>
+        <v>495313</v>
       </c>
       <c r="R25" t="n">
-        <v>6991892</v>
+        <v>6991949</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495688</v>
+        <v>121495706</v>
       </c>
       <c r="B26" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495370</v>
+        <v>495276</v>
       </c>
       <c r="R26" t="n">
-        <v>6991950</v>
+        <v>6991998</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495722</v>
+        <v>121495699</v>
       </c>
       <c r="B27" t="n">
-        <v>97108</v>
+        <v>90248</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221063</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495023</v>
+        <v>495037</v>
       </c>
       <c r="R27" t="n">
-        <v>6991790</v>
+        <v>6991941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495683</v>
+        <v>121495701</v>
       </c>
       <c r="B28" t="n">
-        <v>91978</v>
+        <v>101267</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495158</v>
+        <v>495371</v>
       </c>
       <c r="R28" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495700</v>
+        <v>121495710</v>
       </c>
       <c r="B29" t="n">
-        <v>92019</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,25 +3766,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495333</v>
+        <v>494983</v>
       </c>
       <c r="R29" t="n">
-        <v>6991958</v>
+        <v>6991722</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495634</v>
+        <v>121495654</v>
       </c>
       <c r="B30" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495050</v>
+        <v>495089</v>
       </c>
       <c r="R30" t="n">
-        <v>6992120</v>
+        <v>6992087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495702</v>
+        <v>121495726</v>
       </c>
       <c r="B31" t="n">
-        <v>103609</v>
+        <v>103612</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495369</v>
+        <v>494938</v>
       </c>
       <c r="R31" t="n">
-        <v>6991950</v>
+        <v>6991772</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495710</v>
+        <v>121495688</v>
       </c>
       <c r="B32" t="n">
-        <v>98095</v>
+        <v>100364</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494983</v>
+        <v>495370</v>
       </c>
       <c r="R32" t="n">
-        <v>6991722</v>
+        <v>6991950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495701</v>
+        <v>121495683</v>
       </c>
       <c r="B33" t="n">
-        <v>101264</v>
+        <v>91981</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495371</v>
+        <v>495158</v>
       </c>
       <c r="R33" t="n">
-        <v>6991950</v>
+        <v>6991970</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495695</v>
+        <v>121495693</v>
       </c>
       <c r="B34" t="n">
-        <v>92019</v>
+        <v>103612</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495069</v>
+        <v>495317</v>
       </c>
       <c r="R34" t="n">
-        <v>6991736</v>
+        <v>6991944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495712</v>
+        <v>121495725</v>
       </c>
       <c r="B35" t="n">
-        <v>100270</v>
+        <v>103612</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495313</v>
+        <v>494962</v>
       </c>
       <c r="R35" t="n">
-        <v>6991949</v>
+        <v>6991783</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495693</v>
+        <v>121495746</v>
       </c>
       <c r="B36" t="n">
-        <v>103609</v>
+        <v>90175</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,25 +4480,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>3286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495317</v>
+        <v>495314</v>
       </c>
       <c r="R36" t="n">
-        <v>6991944</v>
+        <v>6991947</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495697</v>
+        <v>121495715</v>
       </c>
       <c r="B37" t="n">
-        <v>101264</v>
+        <v>90248</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4613,7 +4613,7 @@
         <v>495040</v>
       </c>
       <c r="R37" t="n">
-        <v>6991930</v>
+        <v>6991932</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495715</v>
+        <v>121495700</v>
       </c>
       <c r="B38" t="n">
-        <v>90245</v>
+        <v>92022</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495040</v>
+        <v>495333</v>
       </c>
       <c r="R38" t="n">
-        <v>6991932</v>
+        <v>6991958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495694</v>
+        <v>121495713</v>
       </c>
       <c r="B39" t="n">
-        <v>103609</v>
+        <v>101267</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,21 +4790,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495054</v>
+        <v>494943</v>
       </c>
       <c r="R39" t="n">
-        <v>6991738</v>
+        <v>6991755</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495682</v>
+        <v>121495689</v>
       </c>
       <c r="B40" t="n">
-        <v>103609</v>
+        <v>90248</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4888,25 +4888,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495314</v>
+        <v>495313</v>
       </c>
       <c r="R40" t="n">
-        <v>6991997</v>
+        <v>6991964</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495713</v>
+        <v>121495702</v>
       </c>
       <c r="B41" t="n">
-        <v>101264</v>
+        <v>103612</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494943</v>
+        <v>495369</v>
       </c>
       <c r="R41" t="n">
-        <v>6991755</v>
+        <v>6991950</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495696</v>
+        <v>121495659</v>
       </c>
       <c r="B42" t="n">
-        <v>91980</v>
+        <v>100364</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495158</v>
+        <v>494954</v>
       </c>
       <c r="R42" t="n">
-        <v>6991970</v>
+        <v>6992160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495691</v>
+        <v>121495634</v>
       </c>
       <c r="B43" t="n">
-        <v>91643</v>
+        <v>100364</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494951</v>
+        <v>495050</v>
       </c>
       <c r="R43" t="n">
-        <v>6991725</v>
+        <v>6992120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495724</v>
+        <v>121495704</v>
       </c>
       <c r="B44" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495179</v>
+        <v>495047</v>
       </c>
       <c r="R44" t="n">
-        <v>6992005</v>
+        <v>6991920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495709</v>
+        <v>121495694</v>
       </c>
       <c r="B45" t="n">
-        <v>98012</v>
+        <v>103612</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495057</v>
+        <v>495054</v>
       </c>
       <c r="R45" t="n">
-        <v>6991872</v>
+        <v>6991738</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495746</v>
+        <v>121495716</v>
       </c>
       <c r="B46" t="n">
-        <v>90172</v>
+        <v>92020</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495314</v>
+        <v>495158</v>
       </c>
       <c r="R46" t="n">
-        <v>6991947</v>
+        <v>6991970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495704</v>
+        <v>121495723</v>
       </c>
       <c r="B47" t="n">
-        <v>98095</v>
+        <v>92022</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495047</v>
+        <v>494964</v>
       </c>
       <c r="R47" t="n">
-        <v>6991920</v>
+        <v>6991779</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
         <v>121495686</v>
       </c>
       <c r="B48" t="n">
-        <v>92019</v>
+        <v>92022</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495717</v>
+        <v>121495682</v>
       </c>
       <c r="B49" t="n">
-        <v>100270</v>
+        <v>103612</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495355</v>
+        <v>495314</v>
       </c>
       <c r="R49" t="n">
-        <v>6991976</v>
+        <v>6991997</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495706</v>
+        <v>121495691</v>
       </c>
       <c r="B50" t="n">
-        <v>100361</v>
+        <v>91646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495276</v>
+        <v>494951</v>
       </c>
       <c r="R50" t="n">
-        <v>6991998</v>
+        <v>6991725</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495659</v>
+        <v>121495696</v>
       </c>
       <c r="B51" t="n">
-        <v>100361</v>
+        <v>91983</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494954</v>
+        <v>495158</v>
       </c>
       <c r="R51" t="n">
-        <v>6992160</v>
+        <v>6991970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495654</v>
+        <v>121495722</v>
       </c>
       <c r="B52" t="n">
-        <v>100361</v>
+        <v>97111</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221063</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495089</v>
+        <v>495023</v>
       </c>
       <c r="R52" t="n">
-        <v>6992087</v>
+        <v>6991790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495684</v>
+        <v>121495697</v>
       </c>
       <c r="B53" t="n">
-        <v>101264</v>
+        <v>101267</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495352</v>
+        <v>495040</v>
       </c>
       <c r="R53" t="n">
-        <v>6991979</v>
+        <v>6991930</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495726</v>
+        <v>121495695</v>
       </c>
       <c r="B54" t="n">
-        <v>103609</v>
+        <v>92022</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494938</v>
+        <v>495069</v>
       </c>
       <c r="R54" t="n">
-        <v>6991772</v>
+        <v>6991736</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495689</v>
+        <v>121495705</v>
       </c>
       <c r="B55" t="n">
-        <v>90245</v>
+        <v>92022</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495313</v>
+        <v>495117</v>
       </c>
       <c r="R55" t="n">
-        <v>6991964</v>
+        <v>6991892</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495725</v>
+        <v>121495709</v>
       </c>
       <c r="B56" t="n">
-        <v>103609</v>
+        <v>98015</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494962</v>
+        <v>495057</v>
       </c>
       <c r="R56" t="n">
-        <v>6991783</v>
+        <v>6991872</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495716</v>
+        <v>121495684</v>
       </c>
       <c r="B57" t="n">
-        <v>92017</v>
+        <v>101267</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1968</v>
+        <v>221235</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495158</v>
+        <v>495352</v>
       </c>
       <c r="R57" t="n">
-        <v>6991970</v>
+        <v>6991979</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495699</v>
+        <v>121495717</v>
       </c>
       <c r="B58" t="n">
-        <v>90245</v>
+        <v>100273</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,25 +6724,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495037</v>
+        <v>495355</v>
       </c>
       <c r="R58" t="n">
-        <v>6991941</v>
+        <v>6991976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>91983</v>
+        <v>90248</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R22" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>90248</v>
+        <v>91983</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R23" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495724</v>
+        <v>121495659</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495179</v>
+        <v>494954</v>
       </c>
       <c r="R24" t="n">
-        <v>6992005</v>
+        <v>6992160</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495712</v>
+        <v>121495693</v>
       </c>
       <c r="B25" t="n">
-        <v>100273</v>
+        <v>103612</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,16 +3362,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495313</v>
+        <v>495317</v>
       </c>
       <c r="R25" t="n">
-        <v>6991949</v>
+        <v>6991944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495706</v>
+        <v>121495710</v>
       </c>
       <c r="B26" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495276</v>
+        <v>494983</v>
       </c>
       <c r="R26" t="n">
-        <v>6991998</v>
+        <v>6991722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495699</v>
+        <v>121495725</v>
       </c>
       <c r="B27" t="n">
-        <v>90248</v>
+        <v>103612</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495037</v>
+        <v>494962</v>
       </c>
       <c r="R27" t="n">
-        <v>6991941</v>
+        <v>6991783</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495701</v>
+        <v>121495695</v>
       </c>
       <c r="B28" t="n">
-        <v>101267</v>
+        <v>92022</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495371</v>
+        <v>495069</v>
       </c>
       <c r="R28" t="n">
-        <v>6991950</v>
+        <v>6991736</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495710</v>
+        <v>121495686</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>92022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,25 +3766,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494983</v>
+        <v>494949</v>
       </c>
       <c r="R29" t="n">
-        <v>6991722</v>
+        <v>6991727</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495654</v>
+        <v>121495705</v>
       </c>
       <c r="B30" t="n">
-        <v>100364</v>
+        <v>92022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495089</v>
+        <v>495117</v>
       </c>
       <c r="R30" t="n">
-        <v>6992087</v>
+        <v>6991892</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495726</v>
+        <v>121495696</v>
       </c>
       <c r="B31" t="n">
-        <v>103612</v>
+        <v>91983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494938</v>
+        <v>495158</v>
       </c>
       <c r="R31" t="n">
-        <v>6991772</v>
+        <v>6991970</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495688</v>
+        <v>121495654</v>
       </c>
       <c r="B32" t="n">
         <v>100364</v>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495370</v>
+        <v>495089</v>
       </c>
       <c r="R32" t="n">
-        <v>6991950</v>
+        <v>6992087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495683</v>
+        <v>121495702</v>
       </c>
       <c r="B33" t="n">
-        <v>91981</v>
+        <v>103612</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>222412</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495158</v>
+        <v>495369</v>
       </c>
       <c r="R33" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495693</v>
+        <v>121495726</v>
       </c>
       <c r="B34" t="n">
         <v>103612</v>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495317</v>
+        <v>494938</v>
       </c>
       <c r="R34" t="n">
-        <v>6991944</v>
+        <v>6991772</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495725</v>
+        <v>121495723</v>
       </c>
       <c r="B35" t="n">
-        <v>103612</v>
+        <v>92022</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494962</v>
+        <v>494964</v>
       </c>
       <c r="R35" t="n">
-        <v>6991783</v>
+        <v>6991779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495746</v>
+        <v>121495699</v>
       </c>
       <c r="B36" t="n">
-        <v>90175</v>
+        <v>90248</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,25 +4480,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495314</v>
+        <v>495037</v>
       </c>
       <c r="R36" t="n">
-        <v>6991947</v>
+        <v>6991941</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495715</v>
+        <v>121495706</v>
       </c>
       <c r="B37" t="n">
-        <v>90248</v>
+        <v>100364</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495040</v>
+        <v>495276</v>
       </c>
       <c r="R37" t="n">
-        <v>6991932</v>
+        <v>6991998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495700</v>
+        <v>121495722</v>
       </c>
       <c r="B38" t="n">
-        <v>92022</v>
+        <v>97111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4688,21 +4688,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>221063</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495333</v>
+        <v>495023</v>
       </c>
       <c r="R38" t="n">
-        <v>6991958</v>
+        <v>6991790</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495713</v>
+        <v>121495691</v>
       </c>
       <c r="B39" t="n">
-        <v>101267</v>
+        <v>91646</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,21 +4790,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494943</v>
+        <v>494951</v>
       </c>
       <c r="R39" t="n">
-        <v>6991755</v>
+        <v>6991725</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495689</v>
+        <v>121495704</v>
       </c>
       <c r="B40" t="n">
-        <v>90248</v>
+        <v>98098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495313</v>
+        <v>495047</v>
       </c>
       <c r="R40" t="n">
-        <v>6991964</v>
+        <v>6991920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495702</v>
+        <v>121495697</v>
       </c>
       <c r="B41" t="n">
-        <v>103612</v>
+        <v>101267</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495369</v>
+        <v>495040</v>
       </c>
       <c r="R41" t="n">
-        <v>6991950</v>
+        <v>6991930</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495659</v>
+        <v>121495709</v>
       </c>
       <c r="B42" t="n">
-        <v>100364</v>
+        <v>98015</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494954</v>
+        <v>495057</v>
       </c>
       <c r="R42" t="n">
-        <v>6992160</v>
+        <v>6991872</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495634</v>
+        <v>121495713</v>
       </c>
       <c r="B43" t="n">
-        <v>100364</v>
+        <v>101267</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495050</v>
+        <v>494943</v>
       </c>
       <c r="R43" t="n">
-        <v>6992120</v>
+        <v>6991755</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495704</v>
+        <v>121495715</v>
       </c>
       <c r="B44" t="n">
-        <v>98098</v>
+        <v>90248</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5747</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495047</v>
+        <v>495040</v>
       </c>
       <c r="R44" t="n">
-        <v>6991920</v>
+        <v>6991932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495694</v>
+        <v>121495684</v>
       </c>
       <c r="B45" t="n">
-        <v>103612</v>
+        <v>101267</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495054</v>
+        <v>495352</v>
       </c>
       <c r="R45" t="n">
-        <v>6991738</v>
+        <v>6991979</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495716</v>
+        <v>121495712</v>
       </c>
       <c r="B46" t="n">
-        <v>92020</v>
+        <v>100273</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1968</v>
+        <v>222771</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495158</v>
+        <v>495313</v>
       </c>
       <c r="R46" t="n">
-        <v>6991970</v>
+        <v>6991949</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495723</v>
+        <v>121495701</v>
       </c>
       <c r="B47" t="n">
-        <v>92022</v>
+        <v>101267</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494964</v>
+        <v>495371</v>
       </c>
       <c r="R47" t="n">
-        <v>6991779</v>
+        <v>6991950</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495686</v>
+        <v>121495694</v>
       </c>
       <c r="B48" t="n">
-        <v>92022</v>
+        <v>103612</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494949</v>
+        <v>495054</v>
       </c>
       <c r="R48" t="n">
-        <v>6991727</v>
+        <v>6991738</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495691</v>
+        <v>121495746</v>
       </c>
       <c r="B50" t="n">
-        <v>91646</v>
+        <v>90175</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,25 +5908,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494951</v>
+        <v>495314</v>
       </c>
       <c r="R50" t="n">
-        <v>6991725</v>
+        <v>6991947</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495696</v>
+        <v>121495688</v>
       </c>
       <c r="B51" t="n">
-        <v>91983</v>
+        <v>100364</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495158</v>
+        <v>495370</v>
       </c>
       <c r="R51" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495722</v>
+        <v>121495717</v>
       </c>
       <c r="B52" t="n">
-        <v>97111</v>
+        <v>100273</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221063</v>
+        <v>222771</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495023</v>
+        <v>495355</v>
       </c>
       <c r="R52" t="n">
-        <v>6991790</v>
+        <v>6991976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495697</v>
+        <v>121495700</v>
       </c>
       <c r="B53" t="n">
-        <v>101267</v>
+        <v>92022</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495040</v>
+        <v>495333</v>
       </c>
       <c r="R53" t="n">
-        <v>6991930</v>
+        <v>6991958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495695</v>
+        <v>121495683</v>
       </c>
       <c r="B54" t="n">
-        <v>92022</v>
+        <v>91981</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495069</v>
+        <v>495158</v>
       </c>
       <c r="R54" t="n">
-        <v>6991736</v>
+        <v>6991970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495705</v>
+        <v>121495724</v>
       </c>
       <c r="B55" t="n">
-        <v>92022</v>
+        <v>98098</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495117</v>
+        <v>495179</v>
       </c>
       <c r="R55" t="n">
-        <v>6991892</v>
+        <v>6992005</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495709</v>
+        <v>121495689</v>
       </c>
       <c r="B56" t="n">
-        <v>98015</v>
+        <v>90248</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495057</v>
+        <v>495313</v>
       </c>
       <c r="R56" t="n">
-        <v>6991872</v>
+        <v>6991964</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495684</v>
+        <v>121495716</v>
       </c>
       <c r="B57" t="n">
-        <v>101267</v>
+        <v>92020</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221235</v>
+        <v>1968</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495352</v>
+        <v>495158</v>
       </c>
       <c r="R57" t="n">
-        <v>6991979</v>
+        <v>6991970</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495717</v>
+        <v>121495634</v>
       </c>
       <c r="B58" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495355</v>
+        <v>495050</v>
       </c>
       <c r="R58" t="n">
-        <v>6991976</v>
+        <v>6992120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495709</v>
+        <v>121495713</v>
       </c>
       <c r="B42" t="n">
-        <v>98015</v>
+        <v>101267</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>221235</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495057</v>
+        <v>494943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991872</v>
+        <v>6991755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495713</v>
+        <v>121495709</v>
       </c>
       <c r="B43" t="n">
-        <v>101267</v>
+        <v>98015</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221235</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494943</v>
+        <v>495057</v>
       </c>
       <c r="R43" t="n">
-        <v>6991755</v>
+        <v>6991872</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495683</v>
+        <v>121495724</v>
       </c>
       <c r="B54" t="n">
-        <v>91981</v>
+        <v>98098</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495158</v>
+        <v>495179</v>
       </c>
       <c r="R54" t="n">
-        <v>6991970</v>
+        <v>6992005</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495724</v>
+        <v>121495683</v>
       </c>
       <c r="B55" t="n">
-        <v>98098</v>
+        <v>91981</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495179</v>
+        <v>495158</v>
       </c>
       <c r="R55" t="n">
-        <v>6992005</v>
+        <v>6991970</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495695</v>
+        <v>121495654</v>
       </c>
       <c r="B28" t="n">
-        <v>92022</v>
+        <v>100364</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495069</v>
+        <v>495089</v>
       </c>
       <c r="R28" t="n">
-        <v>6991736</v>
+        <v>6992087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495686</v>
+        <v>121495702</v>
       </c>
       <c r="B29" t="n">
-        <v>92022</v>
+        <v>103612</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494949</v>
+        <v>495369</v>
       </c>
       <c r="R29" t="n">
-        <v>6991727</v>
+        <v>6991950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495705</v>
+        <v>121495695</v>
       </c>
       <c r="B30" t="n">
         <v>92022</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495117</v>
+        <v>495069</v>
       </c>
       <c r="R30" t="n">
-        <v>6991892</v>
+        <v>6991736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495696</v>
+        <v>121495686</v>
       </c>
       <c r="B31" t="n">
-        <v>91983</v>
+        <v>92022</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495158</v>
+        <v>494949</v>
       </c>
       <c r="R31" t="n">
-        <v>6991970</v>
+        <v>6991727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495654</v>
+        <v>121495705</v>
       </c>
       <c r="B32" t="n">
-        <v>100364</v>
+        <v>92022</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495089</v>
+        <v>495117</v>
       </c>
       <c r="R32" t="n">
-        <v>6992087</v>
+        <v>6991892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495702</v>
+        <v>121495696</v>
       </c>
       <c r="B33" t="n">
-        <v>103612</v>
+        <v>91983</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222412</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495369</v>
+        <v>495158</v>
       </c>
       <c r="R33" t="n">
-        <v>6991950</v>
+        <v>6991970</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495704</v>
+        <v>121495697</v>
       </c>
       <c r="B40" t="n">
-        <v>98098</v>
+        <v>101267</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4888,25 +4888,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495047</v>
+        <v>495040</v>
       </c>
       <c r="R40" t="n">
-        <v>6991920</v>
+        <v>6991930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495697</v>
+        <v>121495704</v>
       </c>
       <c r="B41" t="n">
-        <v>101267</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495040</v>
+        <v>495047</v>
       </c>
       <c r="R41" t="n">
-        <v>6991930</v>
+        <v>6991920</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495724</v>
+        <v>121495683</v>
       </c>
       <c r="B54" t="n">
-        <v>98098</v>
+        <v>91981</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495179</v>
+        <v>495158</v>
       </c>
       <c r="R54" t="n">
-        <v>6992005</v>
+        <v>6991970</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495683</v>
+        <v>121495724</v>
       </c>
       <c r="B55" t="n">
-        <v>91981</v>
+        <v>98098</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495158</v>
+        <v>495179</v>
       </c>
       <c r="R55" t="n">
-        <v>6991970</v>
+        <v>6992005</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90248</v>
+        <v>90254</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>90248</v>
+        <v>90254</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>91983</v>
+        <v>91989</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495659</v>
+        <v>121495715</v>
       </c>
       <c r="B24" t="n">
-        <v>100364</v>
+        <v>90254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494954</v>
+        <v>495040</v>
       </c>
       <c r="R24" t="n">
-        <v>6992160</v>
+        <v>6991932</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495693</v>
+        <v>121495704</v>
       </c>
       <c r="B25" t="n">
-        <v>103612</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495317</v>
+        <v>495047</v>
       </c>
       <c r="R25" t="n">
-        <v>6991944</v>
+        <v>6991920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495710</v>
+        <v>121495705</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>92028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494983</v>
+        <v>495117</v>
       </c>
       <c r="R26" t="n">
-        <v>6991722</v>
+        <v>6991892</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495725</v>
+        <v>121495724</v>
       </c>
       <c r="B27" t="n">
-        <v>103612</v>
+        <v>98104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494962</v>
+        <v>495179</v>
       </c>
       <c r="R27" t="n">
-        <v>6991783</v>
+        <v>6992005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495654</v>
+        <v>121495725</v>
       </c>
       <c r="B28" t="n">
-        <v>100364</v>
+        <v>103618</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495089</v>
+        <v>494962</v>
       </c>
       <c r="R28" t="n">
-        <v>6992087</v>
+        <v>6991783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495702</v>
+        <v>121495717</v>
       </c>
       <c r="B29" t="n">
-        <v>103612</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495369</v>
+        <v>495355</v>
       </c>
       <c r="R29" t="n">
-        <v>6991950</v>
+        <v>6991976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495695</v>
+        <v>121495723</v>
       </c>
       <c r="B30" t="n">
-        <v>92022</v>
+        <v>92028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495069</v>
+        <v>494964</v>
       </c>
       <c r="R30" t="n">
-        <v>6991736</v>
+        <v>6991779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495686</v>
+        <v>121495713</v>
       </c>
       <c r="B31" t="n">
-        <v>92022</v>
+        <v>101273</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494949</v>
+        <v>494943</v>
       </c>
       <c r="R31" t="n">
-        <v>6991727</v>
+        <v>6991755</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495705</v>
+        <v>121495706</v>
       </c>
       <c r="B32" t="n">
-        <v>92022</v>
+        <v>100370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495117</v>
+        <v>495276</v>
       </c>
       <c r="R32" t="n">
-        <v>6991892</v>
+        <v>6991998</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495696</v>
+        <v>121495688</v>
       </c>
       <c r="B33" t="n">
-        <v>91983</v>
+        <v>100370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495158</v>
+        <v>495370</v>
       </c>
       <c r="R33" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495726</v>
+        <v>121495709</v>
       </c>
       <c r="B34" t="n">
-        <v>103612</v>
+        <v>98021</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494938</v>
+        <v>495057</v>
       </c>
       <c r="R34" t="n">
-        <v>6991772</v>
+        <v>6991872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495723</v>
+        <v>121495700</v>
       </c>
       <c r="B35" t="n">
-        <v>92022</v>
+        <v>92028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494964</v>
+        <v>495333</v>
       </c>
       <c r="R35" t="n">
-        <v>6991779</v>
+        <v>6991958</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495699</v>
+        <v>121495701</v>
       </c>
       <c r="B36" t="n">
-        <v>90248</v>
+        <v>101273</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,25 +4480,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495037</v>
+        <v>495371</v>
       </c>
       <c r="R36" t="n">
-        <v>6991941</v>
+        <v>6991950</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495706</v>
+        <v>121495696</v>
       </c>
       <c r="B37" t="n">
-        <v>100364</v>
+        <v>91989</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495276</v>
+        <v>495158</v>
       </c>
       <c r="R37" t="n">
-        <v>6991998</v>
+        <v>6991970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495722</v>
+        <v>121495683</v>
       </c>
       <c r="B38" t="n">
-        <v>97111</v>
+        <v>91987</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221063</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495023</v>
+        <v>495158</v>
       </c>
       <c r="R38" t="n">
-        <v>6991790</v>
+        <v>6991970</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495691</v>
+        <v>121495746</v>
       </c>
       <c r="B39" t="n">
-        <v>91646</v>
+        <v>90181</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494951</v>
+        <v>495314</v>
       </c>
       <c r="R39" t="n">
-        <v>6991725</v>
+        <v>6991947</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495697</v>
+        <v>121495654</v>
       </c>
       <c r="B40" t="n">
-        <v>101267</v>
+        <v>100370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495040</v>
+        <v>495089</v>
       </c>
       <c r="R40" t="n">
-        <v>6991930</v>
+        <v>6992087</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495704</v>
+        <v>121495726</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>103618</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495047</v>
+        <v>494938</v>
       </c>
       <c r="R41" t="n">
-        <v>6991920</v>
+        <v>6991772</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495713</v>
+        <v>121495722</v>
       </c>
       <c r="B42" t="n">
-        <v>101267</v>
+        <v>97117</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221235</v>
+        <v>221063</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494943</v>
+        <v>495023</v>
       </c>
       <c r="R42" t="n">
-        <v>6991755</v>
+        <v>6991790</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495709</v>
+        <v>121495694</v>
       </c>
       <c r="B43" t="n">
-        <v>98015</v>
+        <v>103618</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495057</v>
+        <v>495054</v>
       </c>
       <c r="R43" t="n">
-        <v>6991872</v>
+        <v>6991738</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495715</v>
+        <v>121495695</v>
       </c>
       <c r="B44" t="n">
-        <v>90248</v>
+        <v>92028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5296,25 +5296,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495040</v>
+        <v>495069</v>
       </c>
       <c r="R44" t="n">
-        <v>6991932</v>
+        <v>6991736</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495684</v>
+        <v>121495699</v>
       </c>
       <c r="B45" t="n">
-        <v>101267</v>
+        <v>90254</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495352</v>
+        <v>495037</v>
       </c>
       <c r="R45" t="n">
-        <v>6991979</v>
+        <v>6991941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495712</v>
+        <v>121495710</v>
       </c>
       <c r="B46" t="n">
-        <v>100273</v>
+        <v>98104</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495313</v>
+        <v>494983</v>
       </c>
       <c r="R46" t="n">
-        <v>6991949</v>
+        <v>6991722</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495701</v>
+        <v>121495684</v>
       </c>
       <c r="B47" t="n">
-        <v>101267</v>
+        <v>101273</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495371</v>
+        <v>495352</v>
       </c>
       <c r="R47" t="n">
-        <v>6991950</v>
+        <v>6991979</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495694</v>
+        <v>121495716</v>
       </c>
       <c r="B48" t="n">
-        <v>103612</v>
+        <v>92026</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222412</v>
+        <v>1968</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495054</v>
+        <v>495158</v>
       </c>
       <c r="R48" t="n">
-        <v>6991738</v>
+        <v>6991970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495682</v>
+        <v>121495686</v>
       </c>
       <c r="B49" t="n">
-        <v>103612</v>
+        <v>92028</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495314</v>
+        <v>494949</v>
       </c>
       <c r="R49" t="n">
-        <v>6991997</v>
+        <v>6991727</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495746</v>
+        <v>121495689</v>
       </c>
       <c r="B50" t="n">
-        <v>90175</v>
+        <v>90254</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,25 +5908,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495314</v>
+        <v>495313</v>
       </c>
       <c r="R50" t="n">
-        <v>6991947</v>
+        <v>6991964</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495688</v>
+        <v>121495659</v>
       </c>
       <c r="B51" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495370</v>
+        <v>494954</v>
       </c>
       <c r="R51" t="n">
-        <v>6991950</v>
+        <v>6992160</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495717</v>
+        <v>121495634</v>
       </c>
       <c r="B52" t="n">
-        <v>100273</v>
+        <v>100370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495355</v>
+        <v>495050</v>
       </c>
       <c r="R52" t="n">
-        <v>6991976</v>
+        <v>6992120</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495700</v>
+        <v>121495712</v>
       </c>
       <c r="B53" t="n">
-        <v>92022</v>
+        <v>100279</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495333</v>
+        <v>495313</v>
       </c>
       <c r="R53" t="n">
-        <v>6991958</v>
+        <v>6991949</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495683</v>
+        <v>121495702</v>
       </c>
       <c r="B54" t="n">
-        <v>91981</v>
+        <v>103618</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495158</v>
+        <v>495369</v>
       </c>
       <c r="R54" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495724</v>
+        <v>121495693</v>
       </c>
       <c r="B55" t="n">
-        <v>98098</v>
+        <v>103618</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495179</v>
+        <v>495317</v>
       </c>
       <c r="R55" t="n">
-        <v>6992005</v>
+        <v>6991944</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495689</v>
+        <v>121495697</v>
       </c>
       <c r="B56" t="n">
-        <v>90248</v>
+        <v>101273</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495313</v>
+        <v>495040</v>
       </c>
       <c r="R56" t="n">
-        <v>6991964</v>
+        <v>6991930</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495716</v>
+        <v>121495691</v>
       </c>
       <c r="B57" t="n">
-        <v>92020</v>
+        <v>91652</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495158</v>
+        <v>494951</v>
       </c>
       <c r="R57" t="n">
-        <v>6991970</v>
+        <v>6991725</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495634</v>
+        <v>121495682</v>
       </c>
       <c r="B58" t="n">
-        <v>100364</v>
+        <v>103618</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495050</v>
+        <v>495314</v>
       </c>
       <c r="R58" t="n">
-        <v>6992120</v>
+        <v>6991997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -1887,7 +1887,7 @@
         <v>103955088</v>
       </c>
       <c r="B12" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>90254</v>
+        <v>90255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495715</v>
+        <v>121495694</v>
       </c>
       <c r="B24" t="n">
-        <v>90254</v>
+        <v>103619</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495040</v>
+        <v>495054</v>
       </c>
       <c r="R24" t="n">
-        <v>6991932</v>
+        <v>6991738</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495704</v>
+        <v>121495659</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495047</v>
+        <v>494954</v>
       </c>
       <c r="R25" t="n">
-        <v>6991920</v>
+        <v>6992160</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495705</v>
+        <v>121495686</v>
       </c>
       <c r="B26" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495117</v>
+        <v>494949</v>
       </c>
       <c r="R26" t="n">
-        <v>6991892</v>
+        <v>6991727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495724</v>
+        <v>121495683</v>
       </c>
       <c r="B27" t="n">
-        <v>98104</v>
+        <v>91988</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495179</v>
+        <v>495158</v>
       </c>
       <c r="R27" t="n">
-        <v>6992005</v>
+        <v>6991970</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495725</v>
+        <v>121495689</v>
       </c>
       <c r="B28" t="n">
-        <v>103618</v>
+        <v>90255</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494962</v>
+        <v>495313</v>
       </c>
       <c r="R28" t="n">
-        <v>6991783</v>
+        <v>6991964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495717</v>
+        <v>121495695</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>92029</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495355</v>
+        <v>495069</v>
       </c>
       <c r="R29" t="n">
-        <v>6991976</v>
+        <v>6991736</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495723</v>
+        <v>121495726</v>
       </c>
       <c r="B30" t="n">
-        <v>92028</v>
+        <v>103619</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494964</v>
+        <v>494938</v>
       </c>
       <c r="R30" t="n">
-        <v>6991779</v>
+        <v>6991772</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495713</v>
+        <v>121495688</v>
       </c>
       <c r="B31" t="n">
-        <v>101273</v>
+        <v>100371</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494943</v>
+        <v>495370</v>
       </c>
       <c r="R31" t="n">
-        <v>6991755</v>
+        <v>6991950</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495706</v>
+        <v>121495724</v>
       </c>
       <c r="B32" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495276</v>
+        <v>495179</v>
       </c>
       <c r="R32" t="n">
-        <v>6991998</v>
+        <v>6992005</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495688</v>
+        <v>121495709</v>
       </c>
       <c r="B33" t="n">
-        <v>100370</v>
+        <v>98022</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495370</v>
+        <v>495057</v>
       </c>
       <c r="R33" t="n">
-        <v>6991950</v>
+        <v>6991872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495709</v>
+        <v>121495722</v>
       </c>
       <c r="B34" t="n">
-        <v>98021</v>
+        <v>97118</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495057</v>
+        <v>495023</v>
       </c>
       <c r="R34" t="n">
-        <v>6991872</v>
+        <v>6991790</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495700</v>
+        <v>121495713</v>
       </c>
       <c r="B35" t="n">
-        <v>92028</v>
+        <v>101274</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495333</v>
+        <v>494943</v>
       </c>
       <c r="R35" t="n">
-        <v>6991958</v>
+        <v>6991755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495701</v>
+        <v>121495717</v>
       </c>
       <c r="B36" t="n">
-        <v>101273</v>
+        <v>100280</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495371</v>
+        <v>495355</v>
       </c>
       <c r="R36" t="n">
-        <v>6991950</v>
+        <v>6991976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495696</v>
+        <v>121495702</v>
       </c>
       <c r="B37" t="n">
-        <v>91989</v>
+        <v>103619</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495158</v>
+        <v>495369</v>
       </c>
       <c r="R37" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495683</v>
+        <v>121495684</v>
       </c>
       <c r="B38" t="n">
-        <v>91987</v>
+        <v>101274</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>221235</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495158</v>
+        <v>495352</v>
       </c>
       <c r="R38" t="n">
-        <v>6991970</v>
+        <v>6991979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495746</v>
+        <v>121495712</v>
       </c>
       <c r="B39" t="n">
-        <v>90181</v>
+        <v>100280</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3286</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495314</v>
+        <v>495313</v>
       </c>
       <c r="R39" t="n">
-        <v>6991947</v>
+        <v>6991949</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495654</v>
+        <v>121495693</v>
       </c>
       <c r="B40" t="n">
-        <v>100370</v>
+        <v>103619</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495089</v>
+        <v>495317</v>
       </c>
       <c r="R40" t="n">
-        <v>6992087</v>
+        <v>6991944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495726</v>
+        <v>121495715</v>
       </c>
       <c r="B41" t="n">
-        <v>103618</v>
+        <v>90255</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494938</v>
+        <v>495040</v>
       </c>
       <c r="R41" t="n">
-        <v>6991772</v>
+        <v>6991932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495722</v>
+        <v>121495700</v>
       </c>
       <c r="B42" t="n">
-        <v>97117</v>
+        <v>92029</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221063</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495023</v>
+        <v>495333</v>
       </c>
       <c r="R42" t="n">
-        <v>6991790</v>
+        <v>6991958</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495694</v>
+        <v>121495699</v>
       </c>
       <c r="B43" t="n">
-        <v>103618</v>
+        <v>90255</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5194,25 +5194,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495054</v>
+        <v>495037</v>
       </c>
       <c r="R43" t="n">
-        <v>6991738</v>
+        <v>6991941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495695</v>
+        <v>121495691</v>
       </c>
       <c r="B44" t="n">
-        <v>92028</v>
+        <v>91653</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495069</v>
+        <v>494951</v>
       </c>
       <c r="R44" t="n">
-        <v>6991736</v>
+        <v>6991725</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495699</v>
+        <v>121495704</v>
       </c>
       <c r="B45" t="n">
-        <v>90254</v>
+        <v>98105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495037</v>
+        <v>495047</v>
       </c>
       <c r="R45" t="n">
-        <v>6991941</v>
+        <v>6991920</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495710</v>
+        <v>121495682</v>
       </c>
       <c r="B46" t="n">
-        <v>98104</v>
+        <v>103619</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494983</v>
+        <v>495314</v>
       </c>
       <c r="R46" t="n">
-        <v>6991722</v>
+        <v>6991997</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495684</v>
+        <v>121495696</v>
       </c>
       <c r="B47" t="n">
-        <v>101273</v>
+        <v>91990</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221235</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495352</v>
+        <v>495158</v>
       </c>
       <c r="R47" t="n">
-        <v>6991979</v>
+        <v>6991970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495716</v>
+        <v>121495701</v>
       </c>
       <c r="B48" t="n">
-        <v>92026</v>
+        <v>101274</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1968</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495158</v>
+        <v>495371</v>
       </c>
       <c r="R48" t="n">
-        <v>6991970</v>
+        <v>6991950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495686</v>
+        <v>121495723</v>
       </c>
       <c r="B49" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494949</v>
+        <v>494964</v>
       </c>
       <c r="R49" t="n">
-        <v>6991727</v>
+        <v>6991779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495689</v>
+        <v>121495725</v>
       </c>
       <c r="B50" t="n">
-        <v>90254</v>
+        <v>103619</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,25 +5908,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495313</v>
+        <v>494962</v>
       </c>
       <c r="R50" t="n">
-        <v>6991964</v>
+        <v>6991783</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495659</v>
+        <v>121495697</v>
       </c>
       <c r="B51" t="n">
-        <v>100370</v>
+        <v>101274</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494954</v>
+        <v>495040</v>
       </c>
       <c r="R51" t="n">
-        <v>6992160</v>
+        <v>6991930</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495634</v>
+        <v>121495705</v>
       </c>
       <c r="B52" t="n">
-        <v>100370</v>
+        <v>92029</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495050</v>
+        <v>495117</v>
       </c>
       <c r="R52" t="n">
-        <v>6992120</v>
+        <v>6991892</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495712</v>
+        <v>121495634</v>
       </c>
       <c r="B53" t="n">
-        <v>100279</v>
+        <v>100371</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495313</v>
+        <v>495050</v>
       </c>
       <c r="R53" t="n">
-        <v>6991949</v>
+        <v>6992120</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495702</v>
+        <v>121495746</v>
       </c>
       <c r="B54" t="n">
-        <v>103618</v>
+        <v>90182</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>3286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495369</v>
+        <v>495314</v>
       </c>
       <c r="R54" t="n">
-        <v>6991950</v>
+        <v>6991947</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495693</v>
+        <v>121495710</v>
       </c>
       <c r="B55" t="n">
-        <v>103618</v>
+        <v>98105</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495317</v>
+        <v>494983</v>
       </c>
       <c r="R55" t="n">
-        <v>6991944</v>
+        <v>6991722</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495697</v>
+        <v>121495716</v>
       </c>
       <c r="B56" t="n">
-        <v>101273</v>
+        <v>92027</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221235</v>
+        <v>1968</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495040</v>
+        <v>495158</v>
       </c>
       <c r="R56" t="n">
-        <v>6991930</v>
+        <v>6991970</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495691</v>
+        <v>121495654</v>
       </c>
       <c r="B57" t="n">
-        <v>91652</v>
+        <v>100371</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494951</v>
+        <v>495089</v>
       </c>
       <c r="R57" t="n">
-        <v>6991725</v>
+        <v>6992087</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6680,12 +6680,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495682</v>
+        <v>121495706</v>
       </c>
       <c r="B58" t="n">
-        <v>103618</v>
+        <v>100371</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495314</v>
+        <v>495276</v>
       </c>
       <c r="R58" t="n">
-        <v>6991997</v>
+        <v>6991998</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495694</v>
+        <v>121495723</v>
       </c>
       <c r="B24" t="n">
-        <v>103619</v>
+        <v>92029</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495054</v>
+        <v>494964</v>
       </c>
       <c r="R24" t="n">
-        <v>6991738</v>
+        <v>6991779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495659</v>
+        <v>121495684</v>
       </c>
       <c r="B25" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494954</v>
+        <v>495352</v>
       </c>
       <c r="R25" t="n">
-        <v>6992160</v>
+        <v>6991979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495686</v>
+        <v>121495716</v>
       </c>
       <c r="B26" t="n">
-        <v>92029</v>
+        <v>92027</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494949</v>
+        <v>495158</v>
       </c>
       <c r="R26" t="n">
-        <v>6991727</v>
+        <v>6991970</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495683</v>
+        <v>121495693</v>
       </c>
       <c r="B27" t="n">
-        <v>91988</v>
+        <v>103619</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495158</v>
+        <v>495317</v>
       </c>
       <c r="R27" t="n">
-        <v>6991970</v>
+        <v>6991944</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495689</v>
+        <v>121495701</v>
       </c>
       <c r="B28" t="n">
-        <v>90255</v>
+        <v>101274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495313</v>
+        <v>495371</v>
       </c>
       <c r="R28" t="n">
-        <v>6991964</v>
+        <v>6991950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495695</v>
+        <v>121495702</v>
       </c>
       <c r="B29" t="n">
-        <v>92029</v>
+        <v>103619</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495069</v>
+        <v>495369</v>
       </c>
       <c r="R29" t="n">
-        <v>6991736</v>
+        <v>6991950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495726</v>
+        <v>121495709</v>
       </c>
       <c r="B30" t="n">
-        <v>103619</v>
+        <v>98022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494938</v>
+        <v>495057</v>
       </c>
       <c r="R30" t="n">
-        <v>6991772</v>
+        <v>6991872</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495688</v>
+        <v>121495689</v>
       </c>
       <c r="B31" t="n">
-        <v>100371</v>
+        <v>90255</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495370</v>
+        <v>495313</v>
       </c>
       <c r="R31" t="n">
-        <v>6991950</v>
+        <v>6991964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495724</v>
+        <v>121495691</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>91653</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495179</v>
+        <v>494951</v>
       </c>
       <c r="R32" t="n">
-        <v>6992005</v>
+        <v>6991725</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495709</v>
+        <v>121495704</v>
       </c>
       <c r="B33" t="n">
-        <v>98022</v>
+        <v>98105</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495057</v>
+        <v>495047</v>
       </c>
       <c r="R33" t="n">
-        <v>6991872</v>
+        <v>6991920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495722</v>
+        <v>121495710</v>
       </c>
       <c r="B34" t="n">
-        <v>97118</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221063</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495023</v>
+        <v>494983</v>
       </c>
       <c r="R34" t="n">
-        <v>6991790</v>
+        <v>6991722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495713</v>
+        <v>121495712</v>
       </c>
       <c r="B35" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494943</v>
+        <v>495313</v>
       </c>
       <c r="R35" t="n">
-        <v>6991755</v>
+        <v>6991949</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495717</v>
+        <v>121495688</v>
       </c>
       <c r="B36" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495355</v>
+        <v>495370</v>
       </c>
       <c r="R36" t="n">
-        <v>6991976</v>
+        <v>6991950</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495702</v>
+        <v>121495634</v>
       </c>
       <c r="B37" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495369</v>
+        <v>495050</v>
       </c>
       <c r="R37" t="n">
-        <v>6991950</v>
+        <v>6992120</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495684</v>
+        <v>121495724</v>
       </c>
       <c r="B38" t="n">
-        <v>101274</v>
+        <v>98105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495352</v>
+        <v>495179</v>
       </c>
       <c r="R38" t="n">
-        <v>6991979</v>
+        <v>6992005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495712</v>
+        <v>121495699</v>
       </c>
       <c r="B39" t="n">
-        <v>100280</v>
+        <v>90255</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495313</v>
+        <v>495037</v>
       </c>
       <c r="R39" t="n">
-        <v>6991949</v>
+        <v>6991941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495693</v>
+        <v>121495722</v>
       </c>
       <c r="B40" t="n">
-        <v>103619</v>
+        <v>97118</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>221063</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495317</v>
+        <v>495023</v>
       </c>
       <c r="R40" t="n">
-        <v>6991944</v>
+        <v>6991790</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495715</v>
+        <v>121495697</v>
       </c>
       <c r="B41" t="n">
-        <v>90255</v>
+        <v>101274</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
         <v>495040</v>
       </c>
       <c r="R41" t="n">
-        <v>6991932</v>
+        <v>6991930</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495700</v>
+        <v>121495746</v>
       </c>
       <c r="B42" t="n">
-        <v>92029</v>
+        <v>90182</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495333</v>
+        <v>495314</v>
       </c>
       <c r="R42" t="n">
-        <v>6991958</v>
+        <v>6991947</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495699</v>
+        <v>121495695</v>
       </c>
       <c r="B43" t="n">
-        <v>90255</v>
+        <v>92029</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5194,25 +5194,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495037</v>
+        <v>495069</v>
       </c>
       <c r="R43" t="n">
-        <v>6991941</v>
+        <v>6991736</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495691</v>
+        <v>121495686</v>
       </c>
       <c r="B44" t="n">
-        <v>91653</v>
+        <v>92029</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494951</v>
+        <v>494949</v>
       </c>
       <c r="R44" t="n">
-        <v>6991725</v>
+        <v>6991727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495704</v>
+        <v>121495654</v>
       </c>
       <c r="B45" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495047</v>
+        <v>495089</v>
       </c>
       <c r="R45" t="n">
-        <v>6991920</v>
+        <v>6992087</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495682</v>
+        <v>121495659</v>
       </c>
       <c r="B46" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495314</v>
+        <v>494954</v>
       </c>
       <c r="R46" t="n">
-        <v>6991997</v>
+        <v>6992160</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495696</v>
+        <v>121495706</v>
       </c>
       <c r="B47" t="n">
-        <v>91990</v>
+        <v>100371</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495158</v>
+        <v>495276</v>
       </c>
       <c r="R47" t="n">
-        <v>6991970</v>
+        <v>6991998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495701</v>
+        <v>121495725</v>
       </c>
       <c r="B48" t="n">
-        <v>101274</v>
+        <v>103619</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495371</v>
+        <v>494962</v>
       </c>
       <c r="R48" t="n">
-        <v>6991950</v>
+        <v>6991783</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495723</v>
+        <v>121495705</v>
       </c>
       <c r="B49" t="n">
         <v>92029</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494964</v>
+        <v>495117</v>
       </c>
       <c r="R49" t="n">
-        <v>6991779</v>
+        <v>6991892</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495725</v>
+        <v>121495700</v>
       </c>
       <c r="B50" t="n">
-        <v>103619</v>
+        <v>92029</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494962</v>
+        <v>495333</v>
       </c>
       <c r="R50" t="n">
-        <v>6991783</v>
+        <v>6991958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495697</v>
+        <v>121495694</v>
       </c>
       <c r="B51" t="n">
-        <v>101274</v>
+        <v>103619</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495040</v>
+        <v>495054</v>
       </c>
       <c r="R51" t="n">
-        <v>6991930</v>
+        <v>6991738</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495705</v>
+        <v>121495683</v>
       </c>
       <c r="B52" t="n">
-        <v>92029</v>
+        <v>91988</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495117</v>
+        <v>495158</v>
       </c>
       <c r="R52" t="n">
-        <v>6991892</v>
+        <v>6991970</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495634</v>
+        <v>121495713</v>
       </c>
       <c r="B53" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495050</v>
+        <v>494943</v>
       </c>
       <c r="R53" t="n">
-        <v>6992120</v>
+        <v>6991755</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495746</v>
+        <v>121495717</v>
       </c>
       <c r="B54" t="n">
-        <v>90182</v>
+        <v>100280</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3286</v>
+        <v>222771</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495314</v>
+        <v>495355</v>
       </c>
       <c r="R54" t="n">
-        <v>6991947</v>
+        <v>6991976</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495710</v>
+        <v>121495696</v>
       </c>
       <c r="B55" t="n">
-        <v>98105</v>
+        <v>91990</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494983</v>
+        <v>495158</v>
       </c>
       <c r="R55" t="n">
-        <v>6991722</v>
+        <v>6991970</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495716</v>
+        <v>121495682</v>
       </c>
       <c r="B56" t="n">
-        <v>92027</v>
+        <v>103619</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1968</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495158</v>
+        <v>495314</v>
       </c>
       <c r="R56" t="n">
-        <v>6991970</v>
+        <v>6991997</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495654</v>
+        <v>121495715</v>
       </c>
       <c r="B57" t="n">
-        <v>100371</v>
+        <v>90255</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495089</v>
+        <v>495040</v>
       </c>
       <c r="R57" t="n">
-        <v>6992087</v>
+        <v>6991932</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6680,12 +6680,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495706</v>
+        <v>121495726</v>
       </c>
       <c r="B58" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495276</v>
+        <v>494938</v>
       </c>
       <c r="R58" t="n">
-        <v>6991998</v>
+        <v>6991772</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B22" t="n">
-        <v>90255</v>
+        <v>91990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R22" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B23" t="n">
-        <v>91990</v>
+        <v>90255</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R23" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495723</v>
+        <v>121495695</v>
       </c>
       <c r="B24" t="n">
         <v>92029</v>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494964</v>
+        <v>495069</v>
       </c>
       <c r="R24" t="n">
-        <v>6991779</v>
+        <v>6991736</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495684</v>
+        <v>121495709</v>
       </c>
       <c r="B25" t="n">
-        <v>101274</v>
+        <v>98022</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495352</v>
+        <v>495057</v>
       </c>
       <c r="R25" t="n">
-        <v>6991979</v>
+        <v>6991872</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495716</v>
+        <v>121495689</v>
       </c>
       <c r="B26" t="n">
-        <v>92027</v>
+        <v>90255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495158</v>
+        <v>495313</v>
       </c>
       <c r="R26" t="n">
-        <v>6991970</v>
+        <v>6991964</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495693</v>
+        <v>121495694</v>
       </c>
       <c r="B27" t="n">
         <v>103619</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495317</v>
+        <v>495054</v>
       </c>
       <c r="R27" t="n">
-        <v>6991944</v>
+        <v>6991738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495701</v>
+        <v>121495724</v>
       </c>
       <c r="B28" t="n">
-        <v>101274</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495371</v>
+        <v>495179</v>
       </c>
       <c r="R28" t="n">
-        <v>6991950</v>
+        <v>6992005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495702</v>
+        <v>121495684</v>
       </c>
       <c r="B29" t="n">
-        <v>103619</v>
+        <v>101274</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495369</v>
+        <v>495352</v>
       </c>
       <c r="R29" t="n">
-        <v>6991950</v>
+        <v>6991979</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495709</v>
+        <v>121495722</v>
       </c>
       <c r="B30" t="n">
-        <v>98022</v>
+        <v>97118</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495057</v>
+        <v>495023</v>
       </c>
       <c r="R30" t="n">
-        <v>6991872</v>
+        <v>6991790</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495689</v>
+        <v>121495712</v>
       </c>
       <c r="B31" t="n">
-        <v>90255</v>
+        <v>100280</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
         <v>495313</v>
       </c>
       <c r="R31" t="n">
-        <v>6991964</v>
+        <v>6991949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495691</v>
+        <v>121495702</v>
       </c>
       <c r="B32" t="n">
-        <v>91653</v>
+        <v>103619</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494951</v>
+        <v>495369</v>
       </c>
       <c r="R32" t="n">
-        <v>6991725</v>
+        <v>6991950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495704</v>
+        <v>121495696</v>
       </c>
       <c r="B33" t="n">
-        <v>98105</v>
+        <v>91990</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495047</v>
+        <v>495158</v>
       </c>
       <c r="R33" t="n">
-        <v>6991920</v>
+        <v>6991970</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495712</v>
+        <v>121495746</v>
       </c>
       <c r="B35" t="n">
-        <v>100280</v>
+        <v>90182</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>3286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495313</v>
+        <v>495314</v>
       </c>
       <c r="R35" t="n">
-        <v>6991949</v>
+        <v>6991947</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495688</v>
+        <v>121495691</v>
       </c>
       <c r="B36" t="n">
-        <v>100371</v>
+        <v>91653</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495370</v>
+        <v>494951</v>
       </c>
       <c r="R36" t="n">
-        <v>6991950</v>
+        <v>6991725</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495634</v>
+        <v>121495697</v>
       </c>
       <c r="B37" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495050</v>
+        <v>495040</v>
       </c>
       <c r="R37" t="n">
-        <v>6992120</v>
+        <v>6991930</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495724</v>
+        <v>121495705</v>
       </c>
       <c r="B38" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495179</v>
+        <v>495117</v>
       </c>
       <c r="R38" t="n">
-        <v>6992005</v>
+        <v>6991892</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495699</v>
+        <v>121495654</v>
       </c>
       <c r="B39" t="n">
-        <v>90255</v>
+        <v>100371</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495037</v>
+        <v>495089</v>
       </c>
       <c r="R39" t="n">
-        <v>6991941</v>
+        <v>6992087</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495722</v>
+        <v>121495693</v>
       </c>
       <c r="B40" t="n">
-        <v>97118</v>
+        <v>103619</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221063</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495023</v>
+        <v>495317</v>
       </c>
       <c r="R40" t="n">
-        <v>6991790</v>
+        <v>6991944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495697</v>
+        <v>121495683</v>
       </c>
       <c r="B41" t="n">
-        <v>101274</v>
+        <v>91988</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221235</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495040</v>
+        <v>495158</v>
       </c>
       <c r="R41" t="n">
-        <v>6991930</v>
+        <v>6991970</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495746</v>
+        <v>121495659</v>
       </c>
       <c r="B42" t="n">
-        <v>90182</v>
+        <v>100371</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3286</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495314</v>
+        <v>494954</v>
       </c>
       <c r="R42" t="n">
-        <v>6991947</v>
+        <v>6992160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495695</v>
+        <v>121495701</v>
       </c>
       <c r="B43" t="n">
-        <v>92029</v>
+        <v>101274</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495069</v>
+        <v>495371</v>
       </c>
       <c r="R43" t="n">
-        <v>6991736</v>
+        <v>6991950</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495686</v>
+        <v>121495706</v>
       </c>
       <c r="B44" t="n">
-        <v>92029</v>
+        <v>100371</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494949</v>
+        <v>495276</v>
       </c>
       <c r="R44" t="n">
-        <v>6991727</v>
+        <v>6991998</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495654</v>
+        <v>121495717</v>
       </c>
       <c r="B45" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495089</v>
+        <v>495355</v>
       </c>
       <c r="R45" t="n">
-        <v>6992087</v>
+        <v>6991976</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495659</v>
+        <v>121495713</v>
       </c>
       <c r="B46" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494954</v>
+        <v>494943</v>
       </c>
       <c r="R46" t="n">
-        <v>6992160</v>
+        <v>6991755</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495706</v>
+        <v>121495682</v>
       </c>
       <c r="B47" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495276</v>
+        <v>495314</v>
       </c>
       <c r="R47" t="n">
-        <v>6991998</v>
+        <v>6991997</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495705</v>
+        <v>121495716</v>
       </c>
       <c r="B49" t="n">
-        <v>92029</v>
+        <v>92027</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5806,25 +5806,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495117</v>
+        <v>495158</v>
       </c>
       <c r="R49" t="n">
-        <v>6991892</v>
+        <v>6991970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495700</v>
+        <v>121495715</v>
       </c>
       <c r="B50" t="n">
-        <v>92029</v>
+        <v>90255</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,25 +5908,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495333</v>
+        <v>495040</v>
       </c>
       <c r="R50" t="n">
-        <v>6991958</v>
+        <v>6991932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495694</v>
+        <v>121495704</v>
       </c>
       <c r="B51" t="n">
-        <v>103619</v>
+        <v>98105</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495054</v>
+        <v>495047</v>
       </c>
       <c r="R51" t="n">
-        <v>6991738</v>
+        <v>6991920</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495683</v>
+        <v>121495686</v>
       </c>
       <c r="B52" t="n">
-        <v>91988</v>
+        <v>92029</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495158</v>
+        <v>494949</v>
       </c>
       <c r="R52" t="n">
-        <v>6991970</v>
+        <v>6991727</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495713</v>
+        <v>121495723</v>
       </c>
       <c r="B53" t="n">
-        <v>101274</v>
+        <v>92029</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494943</v>
+        <v>494964</v>
       </c>
       <c r="R53" t="n">
-        <v>6991755</v>
+        <v>6991779</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495717</v>
+        <v>121495700</v>
       </c>
       <c r="B54" t="n">
-        <v>100280</v>
+        <v>92029</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495355</v>
+        <v>495333</v>
       </c>
       <c r="R54" t="n">
-        <v>6991976</v>
+        <v>6991958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495696</v>
+        <v>121495699</v>
       </c>
       <c r="B55" t="n">
-        <v>91990</v>
+        <v>90255</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495158</v>
+        <v>495037</v>
       </c>
       <c r="R55" t="n">
-        <v>6991970</v>
+        <v>6991941</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495682</v>
+        <v>121495634</v>
       </c>
       <c r="B56" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495314</v>
+        <v>495050</v>
       </c>
       <c r="R56" t="n">
-        <v>6991997</v>
+        <v>6992120</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495715</v>
+        <v>121495726</v>
       </c>
       <c r="B57" t="n">
-        <v>90255</v>
+        <v>103619</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495040</v>
+        <v>494938</v>
       </c>
       <c r="R57" t="n">
-        <v>6991932</v>
+        <v>6991772</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495726</v>
+        <v>121495688</v>
       </c>
       <c r="B58" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494938</v>
+        <v>495370</v>
       </c>
       <c r="R58" t="n">
-        <v>6991772</v>
+        <v>6991950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3032,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342793</v>
+        <v>121342774</v>
       </c>
       <c r="B22" t="n">
-        <v>91990</v>
+        <v>90255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495144</v>
+        <v>495087</v>
       </c>
       <c r="R22" t="n">
-        <v>6991986</v>
+        <v>6991899</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342774</v>
+        <v>121342793</v>
       </c>
       <c r="B23" t="n">
-        <v>90255</v>
+        <v>91990</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495087</v>
+        <v>495144</v>
       </c>
       <c r="R23" t="n">
-        <v>6991899</v>
+        <v>6991986</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495695</v>
+        <v>121495709</v>
       </c>
       <c r="B24" t="n">
-        <v>92029</v>
+        <v>98022</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495069</v>
+        <v>495057</v>
       </c>
       <c r="R24" t="n">
-        <v>6991736</v>
+        <v>6991872</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495709</v>
+        <v>121495696</v>
       </c>
       <c r="B25" t="n">
-        <v>98022</v>
+        <v>91990</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495057</v>
+        <v>495158</v>
       </c>
       <c r="R25" t="n">
-        <v>6991872</v>
+        <v>6991970</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495689</v>
+        <v>121495726</v>
       </c>
       <c r="B26" t="n">
-        <v>90255</v>
+        <v>103619</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495313</v>
+        <v>494938</v>
       </c>
       <c r="R26" t="n">
-        <v>6991964</v>
+        <v>6991772</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495694</v>
+        <v>121495722</v>
       </c>
       <c r="B27" t="n">
-        <v>103619</v>
+        <v>97118</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>221063</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495054</v>
+        <v>495023</v>
       </c>
       <c r="R27" t="n">
-        <v>6991738</v>
+        <v>6991790</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495724</v>
+        <v>121495700</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495179</v>
+        <v>495333</v>
       </c>
       <c r="R28" t="n">
-        <v>6992005</v>
+        <v>6991958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495684</v>
+        <v>121495716</v>
       </c>
       <c r="B29" t="n">
-        <v>101274</v>
+        <v>92027</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,25 +3766,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495352</v>
+        <v>495158</v>
       </c>
       <c r="R29" t="n">
-        <v>6991979</v>
+        <v>6991970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495722</v>
+        <v>121495682</v>
       </c>
       <c r="B30" t="n">
-        <v>97118</v>
+        <v>103619</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221063</v>
+        <v>222412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495023</v>
+        <v>495314</v>
       </c>
       <c r="R30" t="n">
-        <v>6991790</v>
+        <v>6991997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495712</v>
+        <v>121495695</v>
       </c>
       <c r="B31" t="n">
-        <v>100280</v>
+        <v>92029</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495313</v>
+        <v>495069</v>
       </c>
       <c r="R31" t="n">
-        <v>6991949</v>
+        <v>6991736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495702</v>
+        <v>121495705</v>
       </c>
       <c r="B32" t="n">
-        <v>103619</v>
+        <v>92029</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4076,21 +4076,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495369</v>
+        <v>495117</v>
       </c>
       <c r="R32" t="n">
-        <v>6991950</v>
+        <v>6991892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495696</v>
+        <v>121495717</v>
       </c>
       <c r="B33" t="n">
-        <v>91990</v>
+        <v>100280</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,25 +4174,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495158</v>
+        <v>495355</v>
       </c>
       <c r="R33" t="n">
-        <v>6991970</v>
+        <v>6991976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495710</v>
+        <v>121495688</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,25 +4276,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494983</v>
+        <v>495370</v>
       </c>
       <c r="R34" t="n">
-        <v>6991722</v>
+        <v>6991950</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495691</v>
+        <v>121495683</v>
       </c>
       <c r="B36" t="n">
-        <v>91653</v>
+        <v>91988</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,25 +4480,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494951</v>
+        <v>495158</v>
       </c>
       <c r="R36" t="n">
-        <v>6991725</v>
+        <v>6991970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495697</v>
+        <v>121495725</v>
       </c>
       <c r="B37" t="n">
-        <v>101274</v>
+        <v>103619</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495040</v>
+        <v>494962</v>
       </c>
       <c r="R37" t="n">
-        <v>6991930</v>
+        <v>6991783</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495705</v>
+        <v>121495724</v>
       </c>
       <c r="B38" t="n">
-        <v>92029</v>
+        <v>98105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495117</v>
+        <v>495179</v>
       </c>
       <c r="R38" t="n">
-        <v>6991892</v>
+        <v>6992005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495654</v>
+        <v>121495702</v>
       </c>
       <c r="B39" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,21 +4790,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495089</v>
+        <v>495369</v>
       </c>
       <c r="R39" t="n">
-        <v>6992087</v>
+        <v>6991950</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495693</v>
+        <v>121495659</v>
       </c>
       <c r="B40" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495317</v>
+        <v>494954</v>
       </c>
       <c r="R40" t="n">
-        <v>6991944</v>
+        <v>6992160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495683</v>
+        <v>121495654</v>
       </c>
       <c r="B41" t="n">
-        <v>91988</v>
+        <v>100371</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495158</v>
+        <v>495089</v>
       </c>
       <c r="R41" t="n">
-        <v>6991970</v>
+        <v>6992087</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495659</v>
+        <v>121495701</v>
       </c>
       <c r="B42" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494954</v>
+        <v>495371</v>
       </c>
       <c r="R42" t="n">
-        <v>6992160</v>
+        <v>6991950</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495701</v>
+        <v>121495634</v>
       </c>
       <c r="B43" t="n">
-        <v>101274</v>
+        <v>100371</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495371</v>
+        <v>495050</v>
       </c>
       <c r="R43" t="n">
-        <v>6991950</v>
+        <v>6992120</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495717</v>
+        <v>121495686</v>
       </c>
       <c r="B45" t="n">
-        <v>100280</v>
+        <v>92029</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495355</v>
+        <v>494949</v>
       </c>
       <c r="R45" t="n">
-        <v>6991976</v>
+        <v>6991727</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495713</v>
+        <v>121495699</v>
       </c>
       <c r="B46" t="n">
-        <v>101274</v>
+        <v>90255</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494943</v>
+        <v>495037</v>
       </c>
       <c r="R46" t="n">
-        <v>6991755</v>
+        <v>6991941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495682</v>
+        <v>121495710</v>
       </c>
       <c r="B47" t="n">
-        <v>103619</v>
+        <v>98105</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495314</v>
+        <v>494983</v>
       </c>
       <c r="R47" t="n">
-        <v>6991997</v>
+        <v>6991722</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495725</v>
+        <v>121495704</v>
       </c>
       <c r="B48" t="n">
-        <v>103619</v>
+        <v>98105</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494962</v>
+        <v>495047</v>
       </c>
       <c r="R48" t="n">
-        <v>6991783</v>
+        <v>6991920</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495716</v>
+        <v>121495693</v>
       </c>
       <c r="B49" t="n">
-        <v>92027</v>
+        <v>103619</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5806,25 +5806,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1968</v>
+        <v>222412</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495158</v>
+        <v>495317</v>
       </c>
       <c r="R49" t="n">
-        <v>6991970</v>
+        <v>6991944</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495715</v>
+        <v>121495684</v>
       </c>
       <c r="B50" t="n">
-        <v>90255</v>
+        <v>101274</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,25 +5908,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495040</v>
+        <v>495352</v>
       </c>
       <c r="R50" t="n">
-        <v>6991932</v>
+        <v>6991979</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495704</v>
+        <v>121495691</v>
       </c>
       <c r="B51" t="n">
-        <v>98105</v>
+        <v>91653</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495047</v>
+        <v>494951</v>
       </c>
       <c r="R51" t="n">
-        <v>6991920</v>
+        <v>6991725</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495686</v>
+        <v>121495723</v>
       </c>
       <c r="B52" t="n">
         <v>92029</v>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494949</v>
+        <v>494964</v>
       </c>
       <c r="R52" t="n">
-        <v>6991727</v>
+        <v>6991779</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495723</v>
+        <v>121495697</v>
       </c>
       <c r="B53" t="n">
-        <v>92029</v>
+        <v>101274</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494964</v>
+        <v>495040</v>
       </c>
       <c r="R53" t="n">
-        <v>6991779</v>
+        <v>6991930</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495700</v>
+        <v>121495689</v>
       </c>
       <c r="B54" t="n">
-        <v>92029</v>
+        <v>90255</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495333</v>
+        <v>495313</v>
       </c>
       <c r="R54" t="n">
-        <v>6991958</v>
+        <v>6991964</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495699</v>
+        <v>121495712</v>
       </c>
       <c r="B55" t="n">
-        <v>90255</v>
+        <v>100280</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495037</v>
+        <v>495313</v>
       </c>
       <c r="R55" t="n">
-        <v>6991941</v>
+        <v>6991949</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495634</v>
+        <v>121495713</v>
       </c>
       <c r="B56" t="n">
-        <v>100371</v>
+        <v>101274</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495050</v>
+        <v>494943</v>
       </c>
       <c r="R56" t="n">
-        <v>6992120</v>
+        <v>6991755</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495726</v>
+        <v>121495715</v>
       </c>
       <c r="B57" t="n">
-        <v>103619</v>
+        <v>90255</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494938</v>
+        <v>495040</v>
       </c>
       <c r="R57" t="n">
-        <v>6991772</v>
+        <v>6991932</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495688</v>
+        <v>121495694</v>
       </c>
       <c r="B58" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495370</v>
+        <v>495054</v>
       </c>
       <c r="R58" t="n">
-        <v>6991950</v>
+        <v>6991738</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495686</v>
+        <v>121495710</v>
       </c>
       <c r="B45" t="n">
-        <v>92029</v>
+        <v>98105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494949</v>
+        <v>494983</v>
       </c>
       <c r="R45" t="n">
-        <v>6991727</v>
+        <v>6991722</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495699</v>
+        <v>121495704</v>
       </c>
       <c r="B46" t="n">
-        <v>90255</v>
+        <v>98105</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495037</v>
+        <v>495047</v>
       </c>
       <c r="R46" t="n">
-        <v>6991941</v>
+        <v>6991920</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495710</v>
+        <v>121495686</v>
       </c>
       <c r="B47" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494983</v>
+        <v>494949</v>
       </c>
       <c r="R47" t="n">
-        <v>6991722</v>
+        <v>6991727</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495704</v>
+        <v>121495699</v>
       </c>
       <c r="B48" t="n">
-        <v>98105</v>
+        <v>90255</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5747</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495047</v>
+        <v>495037</v>
       </c>
       <c r="R48" t="n">
-        <v>6991920</v>
+        <v>6991941</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495691</v>
+        <v>121495723</v>
       </c>
       <c r="B51" t="n">
-        <v>91653</v>
+        <v>92029</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494951</v>
+        <v>494964</v>
       </c>
       <c r="R51" t="n">
-        <v>6991725</v>
+        <v>6991779</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495723</v>
+        <v>121495691</v>
       </c>
       <c r="B52" t="n">
-        <v>92029</v>
+        <v>91653</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494964</v>
+        <v>494951</v>
       </c>
       <c r="R52" t="n">
-        <v>6991779</v>
+        <v>6991725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495696</v>
+        <v>121495726</v>
       </c>
       <c r="B25" t="n">
-        <v>91990</v>
+        <v>103619</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495158</v>
+        <v>494938</v>
       </c>
       <c r="R25" t="n">
-        <v>6991970</v>
+        <v>6991772</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495726</v>
+        <v>121495722</v>
       </c>
       <c r="B26" t="n">
-        <v>103619</v>
+        <v>97118</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>221063</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494938</v>
+        <v>495023</v>
       </c>
       <c r="R26" t="n">
-        <v>6991772</v>
+        <v>6991790</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495722</v>
+        <v>121495700</v>
       </c>
       <c r="B27" t="n">
-        <v>97118</v>
+        <v>92029</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221063</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495023</v>
+        <v>495333</v>
       </c>
       <c r="R27" t="n">
-        <v>6991790</v>
+        <v>6991958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495700</v>
+        <v>121495696</v>
       </c>
       <c r="B28" t="n">
-        <v>92029</v>
+        <v>91990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495333</v>
+        <v>495158</v>
       </c>
       <c r="R28" t="n">
-        <v>6991958</v>
+        <v>6991970</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495710</v>
+        <v>121495686</v>
       </c>
       <c r="B45" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5398,25 +5398,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494983</v>
+        <v>494949</v>
       </c>
       <c r="R45" t="n">
-        <v>6991722</v>
+        <v>6991727</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495704</v>
+        <v>121495699</v>
       </c>
       <c r="B46" t="n">
-        <v>98105</v>
+        <v>90255</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5747</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495047</v>
+        <v>495037</v>
       </c>
       <c r="R46" t="n">
-        <v>6991920</v>
+        <v>6991941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495686</v>
+        <v>121495710</v>
       </c>
       <c r="B47" t="n">
-        <v>92029</v>
+        <v>98105</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5602,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494949</v>
+        <v>494983</v>
       </c>
       <c r="R47" t="n">
-        <v>6991727</v>
+        <v>6991722</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495699</v>
+        <v>121495704</v>
       </c>
       <c r="B48" t="n">
-        <v>90255</v>
+        <v>98105</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495037</v>
+        <v>495047</v>
       </c>
       <c r="R48" t="n">
-        <v>6991941</v>
+        <v>6991920</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495723</v>
+        <v>121495691</v>
       </c>
       <c r="B51" t="n">
-        <v>92029</v>
+        <v>91653</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494964</v>
+        <v>494951</v>
       </c>
       <c r="R51" t="n">
-        <v>6991779</v>
+        <v>6991725</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495691</v>
+        <v>121495723</v>
       </c>
       <c r="B52" t="n">
-        <v>91653</v>
+        <v>92029</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494951</v>
+        <v>494964</v>
       </c>
       <c r="R52" t="n">
-        <v>6991725</v>
+        <v>6991779</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495715</v>
+        <v>121495694</v>
       </c>
       <c r="B57" t="n">
-        <v>90255</v>
+        <v>103619</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495040</v>
+        <v>495054</v>
       </c>
       <c r="R57" t="n">
-        <v>6991932</v>
+        <v>6991738</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495694</v>
+        <v>121495715</v>
       </c>
       <c r="B58" t="n">
-        <v>103619</v>
+        <v>90255</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,25 +6724,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495054</v>
+        <v>495040</v>
       </c>
       <c r="R58" t="n">
-        <v>6991738</v>
+        <v>6991932</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495700</v>
+        <v>121495683</v>
       </c>
       <c r="B24" t="n">
-        <v>92037</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495333</v>
+        <v>495158</v>
       </c>
       <c r="R24" t="n">
-        <v>6991958</v>
+        <v>6991970</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495716</v>
+        <v>121495696</v>
       </c>
       <c r="B25" t="n">
-        <v>92035</v>
+        <v>91998</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495706</v>
+        <v>121495694</v>
       </c>
       <c r="B26" t="n">
-        <v>100379</v>
+        <v>103627</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495276</v>
+        <v>495054</v>
       </c>
       <c r="R26" t="n">
-        <v>6991998</v>
+        <v>6991738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495725</v>
+        <v>121495682</v>
       </c>
       <c r="B27" t="n">
         <v>103627</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494962</v>
+        <v>495314</v>
       </c>
       <c r="R27" t="n">
-        <v>6991783</v>
+        <v>6991997</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495710</v>
+        <v>121495725</v>
       </c>
       <c r="B28" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,25 +3664,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494983</v>
+        <v>494962</v>
       </c>
       <c r="R28" t="n">
-        <v>6991722</v>
+        <v>6991783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495684</v>
+        <v>121495723</v>
       </c>
       <c r="B29" t="n">
-        <v>101282</v>
+        <v>92037</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495352</v>
+        <v>494964</v>
       </c>
       <c r="R29" t="n">
-        <v>6991979</v>
+        <v>6991779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495694</v>
+        <v>121495705</v>
       </c>
       <c r="B30" t="n">
-        <v>103627</v>
+        <v>92037</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495054</v>
+        <v>495117</v>
       </c>
       <c r="R30" t="n">
-        <v>6991738</v>
+        <v>6991892</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495726</v>
+        <v>121495700</v>
       </c>
       <c r="B31" t="n">
-        <v>103627</v>
+        <v>92037</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494938</v>
+        <v>495333</v>
       </c>
       <c r="R31" t="n">
-        <v>6991772</v>
+        <v>6991958</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495683</v>
+        <v>121495710</v>
       </c>
       <c r="B32" t="n">
-        <v>91996</v>
+        <v>98113</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495158</v>
+        <v>494983</v>
       </c>
       <c r="R32" t="n">
-        <v>6991970</v>
+        <v>6991722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495705</v>
+        <v>121495709</v>
       </c>
       <c r="B33" t="n">
-        <v>92037</v>
+        <v>98030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495117</v>
+        <v>495057</v>
       </c>
       <c r="R33" t="n">
-        <v>6991892</v>
+        <v>6991872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495702</v>
+        <v>121495659</v>
       </c>
       <c r="B34" t="n">
-        <v>103627</v>
+        <v>100379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495369</v>
+        <v>494954</v>
       </c>
       <c r="R34" t="n">
-        <v>6991950</v>
+        <v>6992160</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495691</v>
+        <v>121495634</v>
       </c>
       <c r="B35" t="n">
-        <v>91661</v>
+        <v>100379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494951</v>
+        <v>495050</v>
       </c>
       <c r="R35" t="n">
-        <v>6991725</v>
+        <v>6992120</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495724</v>
+        <v>121495688</v>
       </c>
       <c r="B36" t="n">
-        <v>98113</v>
+        <v>100379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,25 +4480,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495179</v>
+        <v>495370</v>
       </c>
       <c r="R36" t="n">
-        <v>6992005</v>
+        <v>6991950</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495688</v>
+        <v>121495713</v>
       </c>
       <c r="B37" t="n">
-        <v>100379</v>
+        <v>101282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495370</v>
+        <v>494943</v>
       </c>
       <c r="R37" t="n">
-        <v>6991950</v>
+        <v>6991755</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495686</v>
+        <v>121495715</v>
       </c>
       <c r="B38" t="n">
-        <v>92037</v>
+        <v>90262</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494949</v>
+        <v>495040</v>
       </c>
       <c r="R38" t="n">
-        <v>6991727</v>
+        <v>6991932</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495689</v>
+        <v>121495701</v>
       </c>
       <c r="B39" t="n">
-        <v>90262</v>
+        <v>101282</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495313</v>
+        <v>495371</v>
       </c>
       <c r="R39" t="n">
-        <v>6991964</v>
+        <v>6991950</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495634</v>
+        <v>121495702</v>
       </c>
       <c r="B40" t="n">
-        <v>100379</v>
+        <v>103627</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4892,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495050</v>
+        <v>495369</v>
       </c>
       <c r="R40" t="n">
-        <v>6992120</v>
+        <v>6991950</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495682</v>
+        <v>121495699</v>
       </c>
       <c r="B41" t="n">
-        <v>103627</v>
+        <v>90262</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495314</v>
+        <v>495037</v>
       </c>
       <c r="R41" t="n">
-        <v>6991997</v>
+        <v>6991941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495693</v>
+        <v>121495691</v>
       </c>
       <c r="B42" t="n">
-        <v>103627</v>
+        <v>91661</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495317</v>
+        <v>494951</v>
       </c>
       <c r="R42" t="n">
-        <v>6991944</v>
+        <v>6991725</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495695</v>
+        <v>121495716</v>
       </c>
       <c r="B43" t="n">
-        <v>92037</v>
+        <v>92035</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5194,25 +5194,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495069</v>
+        <v>495158</v>
       </c>
       <c r="R43" t="n">
-        <v>6991736</v>
+        <v>6991970</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495722</v>
+        <v>121495717</v>
       </c>
       <c r="B44" t="n">
-        <v>97126</v>
+        <v>100288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221063</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495023</v>
+        <v>495355</v>
       </c>
       <c r="R44" t="n">
-        <v>6991790</v>
+        <v>6991976</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495712</v>
+        <v>121495686</v>
       </c>
       <c r="B45" t="n">
-        <v>100288</v>
+        <v>92037</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495313</v>
+        <v>494949</v>
       </c>
       <c r="R45" t="n">
-        <v>6991949</v>
+        <v>6991727</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495709</v>
+        <v>121495726</v>
       </c>
       <c r="B47" t="n">
-        <v>98030</v>
+        <v>103627</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495057</v>
+        <v>494938</v>
       </c>
       <c r="R47" t="n">
-        <v>6991872</v>
+        <v>6991772</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495699</v>
+        <v>121495684</v>
       </c>
       <c r="B48" t="n">
-        <v>90262</v>
+        <v>101282</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5704,25 +5704,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495037</v>
+        <v>495352</v>
       </c>
       <c r="R48" t="n">
-        <v>6991941</v>
+        <v>6991979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495717</v>
+        <v>121495724</v>
       </c>
       <c r="B49" t="n">
-        <v>100288</v>
+        <v>98113</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5806,25 +5806,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495355</v>
+        <v>495179</v>
       </c>
       <c r="R49" t="n">
-        <v>6991976</v>
+        <v>6992005</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495723</v>
+        <v>121495654</v>
       </c>
       <c r="B50" t="n">
-        <v>92037</v>
+        <v>100379</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494964</v>
+        <v>495089</v>
       </c>
       <c r="R50" t="n">
-        <v>6991779</v>
+        <v>6992087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495696</v>
+        <v>121495695</v>
       </c>
       <c r="B51" t="n">
-        <v>91998</v>
+        <v>92037</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495158</v>
+        <v>495069</v>
       </c>
       <c r="R51" t="n">
-        <v>6991970</v>
+        <v>6991736</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495659</v>
+        <v>121495722</v>
       </c>
       <c r="B52" t="n">
-        <v>100379</v>
+        <v>97126</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221063</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494954</v>
+        <v>495023</v>
       </c>
       <c r="R52" t="n">
-        <v>6992160</v>
+        <v>6991790</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495654</v>
+        <v>121495712</v>
       </c>
       <c r="B53" t="n">
-        <v>100379</v>
+        <v>100288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495089</v>
+        <v>495313</v>
       </c>
       <c r="R53" t="n">
-        <v>6992087</v>
+        <v>6991949</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,12 +6272,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495713</v>
+        <v>121495704</v>
       </c>
       <c r="B54" t="n">
-        <v>101282</v>
+        <v>98113</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494943</v>
+        <v>495047</v>
       </c>
       <c r="R54" t="n">
-        <v>6991755</v>
+        <v>6991920</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495697</v>
+        <v>121495689</v>
       </c>
       <c r="B55" t="n">
-        <v>101282</v>
+        <v>90262</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495040</v>
+        <v>495313</v>
       </c>
       <c r="R55" t="n">
-        <v>6991930</v>
+        <v>6991964</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495715</v>
+        <v>121495693</v>
       </c>
       <c r="B56" t="n">
-        <v>90262</v>
+        <v>103627</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495040</v>
+        <v>495317</v>
       </c>
       <c r="R56" t="n">
-        <v>6991932</v>
+        <v>6991944</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495704</v>
+        <v>121495697</v>
       </c>
       <c r="B57" t="n">
-        <v>98113</v>
+        <v>101282</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495047</v>
+        <v>495040</v>
       </c>
       <c r="R57" t="n">
-        <v>6991920</v>
+        <v>6991930</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495701</v>
+        <v>121495706</v>
       </c>
       <c r="B58" t="n">
-        <v>101282</v>
+        <v>100379</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495371</v>
+        <v>495276</v>
       </c>
       <c r="R58" t="n">
-        <v>6991950</v>
+        <v>6991998</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3448,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495694</v>
+        <v>121495723</v>
       </c>
       <c r="B26" t="n">
-        <v>103627</v>
+        <v>92037</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495054</v>
+        <v>494964</v>
       </c>
       <c r="R26" t="n">
-        <v>6991738</v>
+        <v>6991779</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495682</v>
+        <v>121495694</v>
       </c>
       <c r="B27" t="n">
         <v>103627</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495314</v>
+        <v>495054</v>
       </c>
       <c r="R27" t="n">
-        <v>6991997</v>
+        <v>6991738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495725</v>
+        <v>121495682</v>
       </c>
       <c r="B28" t="n">
         <v>103627</v>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494962</v>
+        <v>495314</v>
       </c>
       <c r="R28" t="n">
-        <v>6991783</v>
+        <v>6991997</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495723</v>
+        <v>121495725</v>
       </c>
       <c r="B29" t="n">
-        <v>92037</v>
+        <v>103627</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494964</v>
+        <v>494962</v>
       </c>
       <c r="R29" t="n">
-        <v>6991779</v>
+        <v>6991783</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495709</v>
+        <v>121495713</v>
       </c>
       <c r="B33" t="n">
-        <v>98030</v>
+        <v>101282</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495057</v>
+        <v>494943</v>
       </c>
       <c r="R33" t="n">
-        <v>6991872</v>
+        <v>6991755</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495659</v>
+        <v>121495709</v>
       </c>
       <c r="B34" t="n">
-        <v>100379</v>
+        <v>98030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494954</v>
+        <v>495057</v>
       </c>
       <c r="R34" t="n">
-        <v>6992160</v>
+        <v>6991872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,7 +4366,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495634</v>
+        <v>121495659</v>
       </c>
       <c r="B35" t="n">
         <v>100379</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495050</v>
+        <v>494954</v>
       </c>
       <c r="R35" t="n">
-        <v>6992120</v>
+        <v>6992160</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495688</v>
+        <v>121495634</v>
       </c>
       <c r="B36" t="n">
         <v>100379</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495370</v>
+        <v>495050</v>
       </c>
       <c r="R36" t="n">
-        <v>6991950</v>
+        <v>6992120</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495713</v>
+        <v>121495688</v>
       </c>
       <c r="B37" t="n">
-        <v>101282</v>
+        <v>100379</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4586,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494943</v>
+        <v>495370</v>
       </c>
       <c r="R37" t="n">
-        <v>6991755</v>
+        <v>6991950</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495702</v>
+        <v>121495699</v>
       </c>
       <c r="B40" t="n">
-        <v>103627</v>
+        <v>90262</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4888,25 +4888,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495369</v>
+        <v>495037</v>
       </c>
       <c r="R40" t="n">
-        <v>6991950</v>
+        <v>6991941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495699</v>
+        <v>121495702</v>
       </c>
       <c r="B41" t="n">
-        <v>90262</v>
+        <v>103627</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5747</v>
+        <v>222412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495037</v>
+        <v>495369</v>
       </c>
       <c r="R41" t="n">
-        <v>6991941</v>
+        <v>6991950</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -3244,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495683</v>
+        <v>121495696</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495696</v>
+        <v>121495683</v>
       </c>
       <c r="B25" t="n">
-        <v>91998</v>
+        <v>91996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495723</v>
+        <v>121495700</v>
       </c>
       <c r="B26" t="n">
         <v>92037</v>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494964</v>
+        <v>495333</v>
       </c>
       <c r="R26" t="n">
-        <v>6991779</v>
+        <v>6991958</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495694</v>
+        <v>121495713</v>
       </c>
       <c r="B27" t="n">
-        <v>103627</v>
+        <v>101282</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495054</v>
+        <v>494943</v>
       </c>
       <c r="R27" t="n">
-        <v>6991738</v>
+        <v>6991755</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495682</v>
+        <v>121495722</v>
       </c>
       <c r="B28" t="n">
-        <v>103627</v>
+        <v>97126</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>221063</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495314</v>
+        <v>495023</v>
       </c>
       <c r="R28" t="n">
-        <v>6991997</v>
+        <v>6991790</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495725</v>
+        <v>121495697</v>
       </c>
       <c r="B29" t="n">
-        <v>103627</v>
+        <v>101282</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494962</v>
+        <v>495040</v>
       </c>
       <c r="R29" t="n">
-        <v>6991783</v>
+        <v>6991930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495705</v>
+        <v>121495706</v>
       </c>
       <c r="B30" t="n">
-        <v>92037</v>
+        <v>100379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3872,21 +3872,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495117</v>
+        <v>495276</v>
       </c>
       <c r="R30" t="n">
-        <v>6991892</v>
+        <v>6991998</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495700</v>
+        <v>121495693</v>
       </c>
       <c r="B31" t="n">
-        <v>92037</v>
+        <v>103627</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495333</v>
+        <v>495317</v>
       </c>
       <c r="R31" t="n">
-        <v>6991958</v>
+        <v>6991944</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495710</v>
+        <v>121495723</v>
       </c>
       <c r="B32" t="n">
-        <v>98113</v>
+        <v>92037</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,25 +4072,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494983</v>
+        <v>494964</v>
       </c>
       <c r="R32" t="n">
-        <v>6991722</v>
+        <v>6991779</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495713</v>
+        <v>121495705</v>
       </c>
       <c r="B33" t="n">
-        <v>101282</v>
+        <v>92037</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494943</v>
+        <v>495117</v>
       </c>
       <c r="R33" t="n">
-        <v>6991755</v>
+        <v>6991892</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495709</v>
+        <v>121495654</v>
       </c>
       <c r="B34" t="n">
-        <v>98030</v>
+        <v>100379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495057</v>
+        <v>495089</v>
       </c>
       <c r="R34" t="n">
-        <v>6991872</v>
+        <v>6992087</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495659</v>
+        <v>121495701</v>
       </c>
       <c r="B35" t="n">
-        <v>100379</v>
+        <v>101282</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,21 +4382,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494954</v>
+        <v>495371</v>
       </c>
       <c r="R35" t="n">
-        <v>6992160</v>
+        <v>6991950</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4468,10 +4468,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495634</v>
+        <v>121495695</v>
       </c>
       <c r="B36" t="n">
-        <v>100379</v>
+        <v>92037</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495050</v>
+        <v>495069</v>
       </c>
       <c r="R36" t="n">
-        <v>6992120</v>
+        <v>6991736</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495688</v>
+        <v>121495704</v>
       </c>
       <c r="B37" t="n">
-        <v>100379</v>
+        <v>98113</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495370</v>
+        <v>495047</v>
       </c>
       <c r="R37" t="n">
-        <v>6991950</v>
+        <v>6991920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495715</v>
+        <v>121495691</v>
       </c>
       <c r="B38" t="n">
-        <v>90262</v>
+        <v>91661</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,25 +4684,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495040</v>
+        <v>494951</v>
       </c>
       <c r="R38" t="n">
-        <v>6991932</v>
+        <v>6991725</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495701</v>
+        <v>121495689</v>
       </c>
       <c r="B39" t="n">
-        <v>101282</v>
+        <v>90262</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4786,25 +4786,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495371</v>
+        <v>495313</v>
       </c>
       <c r="R39" t="n">
-        <v>6991950</v>
+        <v>6991964</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495699</v>
+        <v>121495717</v>
       </c>
       <c r="B40" t="n">
-        <v>90262</v>
+        <v>100288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4888,25 +4888,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495037</v>
+        <v>495355</v>
       </c>
       <c r="R40" t="n">
-        <v>6991941</v>
+        <v>6991976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495702</v>
+        <v>121495710</v>
       </c>
       <c r="B41" t="n">
-        <v>103627</v>
+        <v>98113</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,25 +4990,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495369</v>
+        <v>494983</v>
       </c>
       <c r="R41" t="n">
-        <v>6991950</v>
+        <v>6991722</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495691</v>
+        <v>121495716</v>
       </c>
       <c r="B42" t="n">
-        <v>91661</v>
+        <v>92035</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5092,25 +5092,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494951</v>
+        <v>495158</v>
       </c>
       <c r="R42" t="n">
-        <v>6991725</v>
+        <v>6991970</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495716</v>
+        <v>121495715</v>
       </c>
       <c r="B43" t="n">
-        <v>92035</v>
+        <v>90262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5194,25 +5194,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495158</v>
+        <v>495040</v>
       </c>
       <c r="R43" t="n">
-        <v>6991970</v>
+        <v>6991932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495717</v>
+        <v>121495709</v>
       </c>
       <c r="B44" t="n">
-        <v>100288</v>
+        <v>98030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495355</v>
+        <v>495057</v>
       </c>
       <c r="R44" t="n">
-        <v>6991976</v>
+        <v>6991872</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495686</v>
+        <v>121495684</v>
       </c>
       <c r="B45" t="n">
-        <v>92037</v>
+        <v>101282</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494949</v>
+        <v>495352</v>
       </c>
       <c r="R45" t="n">
-        <v>6991727</v>
+        <v>6991979</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495746</v>
+        <v>121495686</v>
       </c>
       <c r="B46" t="n">
-        <v>90189</v>
+        <v>92037</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5500,25 +5500,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3286</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495314</v>
+        <v>494949</v>
       </c>
       <c r="R46" t="n">
-        <v>6991947</v>
+        <v>6991727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495726</v>
+        <v>121495634</v>
       </c>
       <c r="B47" t="n">
-        <v>103627</v>
+        <v>100379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494938</v>
+        <v>495050</v>
       </c>
       <c r="R47" t="n">
-        <v>6991772</v>
+        <v>6992120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495684</v>
+        <v>121495725</v>
       </c>
       <c r="B48" t="n">
-        <v>101282</v>
+        <v>103627</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5708,21 +5708,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495352</v>
+        <v>494962</v>
       </c>
       <c r="R48" t="n">
-        <v>6991979</v>
+        <v>6991783</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495724</v>
+        <v>121495694</v>
       </c>
       <c r="B49" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5806,25 +5806,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495179</v>
+        <v>495054</v>
       </c>
       <c r="R49" t="n">
-        <v>6992005</v>
+        <v>6991738</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495654</v>
+        <v>121495702</v>
       </c>
       <c r="B50" t="n">
-        <v>100379</v>
+        <v>103627</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495089</v>
+        <v>495369</v>
       </c>
       <c r="R50" t="n">
-        <v>6992087</v>
+        <v>6991950</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495695</v>
+        <v>121495746</v>
       </c>
       <c r="B51" t="n">
-        <v>92037</v>
+        <v>90189</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>3286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495069</v>
+        <v>495314</v>
       </c>
       <c r="R51" t="n">
-        <v>6991736</v>
+        <v>6991947</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495722</v>
+        <v>121495659</v>
       </c>
       <c r="B52" t="n">
-        <v>97126</v>
+        <v>100379</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221063</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495023</v>
+        <v>494954</v>
       </c>
       <c r="R52" t="n">
-        <v>6991790</v>
+        <v>6992160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495712</v>
+        <v>121495682</v>
       </c>
       <c r="B53" t="n">
-        <v>100288</v>
+        <v>103627</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6218,16 +6218,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495313</v>
+        <v>495314</v>
       </c>
       <c r="R53" t="n">
-        <v>6991949</v>
+        <v>6991997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495704</v>
+        <v>121495726</v>
       </c>
       <c r="B54" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495047</v>
+        <v>494938</v>
       </c>
       <c r="R54" t="n">
-        <v>6991920</v>
+        <v>6991772</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495689</v>
+        <v>121495688</v>
       </c>
       <c r="B55" t="n">
-        <v>90262</v>
+        <v>100379</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495313</v>
+        <v>495370</v>
       </c>
       <c r="R55" t="n">
-        <v>6991964</v>
+        <v>6991950</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495693</v>
+        <v>121495699</v>
       </c>
       <c r="B56" t="n">
-        <v>103627</v>
+        <v>90262</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495317</v>
+        <v>495037</v>
       </c>
       <c r="R56" t="n">
-        <v>6991944</v>
+        <v>6991941</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495697</v>
+        <v>121495724</v>
       </c>
       <c r="B57" t="n">
-        <v>101282</v>
+        <v>98113</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495040</v>
+        <v>495179</v>
       </c>
       <c r="R57" t="n">
-        <v>6991930</v>
+        <v>6992005</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495706</v>
+        <v>121495712</v>
       </c>
       <c r="B58" t="n">
-        <v>100379</v>
+        <v>100288</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495276</v>
+        <v>495313</v>
       </c>
       <c r="R58" t="n">
-        <v>6991998</v>
+        <v>6991949</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90643329</v>
+        <v>90840014</v>
       </c>
       <c r="B2" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_S, Jmt</t>
+          <t>Slåtthornet-Lassmyren_N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494916.8827189269</v>
+        <v>494975</v>
       </c>
       <c r="R2" t="n">
-        <v>6991748.027135895</v>
+        <v>6991964</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,28 +743,17 @@
           <t>2019-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,50 +781,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90840027</v>
+        <v>110156156</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_N, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495040.1813943333</v>
+        <v>495013</v>
       </c>
       <c r="R3" t="n">
-        <v>6991892.963824637</v>
+        <v>6991762</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,11 +877,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -910,26 +886,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90840023</v>
+        <v>110156471</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,17 +921,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_N, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495092.8574027569</v>
+        <v>495223</v>
       </c>
       <c r="R4" t="n">
-        <v>6991890.162768417</v>
+        <v>6991978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,22 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,11 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,64 +998,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90840024</v>
+        <v>121495716</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_N, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495092.8574027569</v>
+        <v>495158</v>
       </c>
       <c r="R5" t="n">
-        <v>6991890.162768417</v>
+        <v>6991970</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,40 +1086,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90840026</v>
+        <v>121495746</v>
       </c>
       <c r="B6" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,37 +1113,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_S, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494920.8886286491</v>
+        <v>495314</v>
       </c>
       <c r="R6" t="n">
-        <v>6991695.864192192</v>
+        <v>6991947</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,78 +1183,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91133104</v>
+        <v>62064305</v>
       </c>
       <c r="B7" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Slåtthornets kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495040.1813943333</v>
+        <v>495345</v>
       </c>
       <c r="R7" t="n">
-        <v>6991892.963824637</v>
+        <v>6991907</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,22 +1264,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Borgsjöveckan 2010: Exk. obj. 145 A. Slåtthornets kalkbarrskog, norra delen,</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,75 +1285,65 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91133094</v>
+        <v>90840027</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Slåtthornet-Lassmyren_N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494974.0029603403</v>
+        <v>495040</v>
       </c>
       <c r="R8" t="n">
-        <v>6991680.814753188</v>
+        <v>6991893</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1478,19 +1373,9 @@
           <t>2019-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,53 +1411,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91133106</v>
+        <v>121495683</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495040.1813943333</v>
+        <v>495158</v>
       </c>
       <c r="R9" t="n">
-        <v>6991892.963824637</v>
+        <v>6991970</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,22 +1476,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,75 +1492,64 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91133097</v>
+        <v>121342793</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Slåttbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494974.0029603403</v>
+        <v>495144</v>
       </c>
       <c r="R10" t="n">
-        <v>6991680.814753188</v>
+        <v>6991986</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1717,22 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,83 +1590,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103955092</v>
+        <v>121495696</v>
       </c>
       <c r="B11" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4405</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slåttbodarna, Lockne, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495022.7483605282</v>
+        <v>495158</v>
       </c>
       <c r="R11" t="n">
-        <v>6991778.249802337</v>
+        <v>6991970</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1841,22 +1674,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,56 +1688,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103955088</v>
+        <v>90643329</v>
       </c>
       <c r="B12" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5747</v>
+        <v>4363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1923,17 +1740,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttbodarna, Jmt</t>
+          <t>Slåtthornet-Lassmyren_S, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495311</v>
+        <v>494917</v>
       </c>
       <c r="R12" t="n">
-        <v>6991959</v>
+        <v>6991748</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1957,87 +1774,90 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110156305</v>
+        <v>62064309</v>
       </c>
       <c r="B13" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lassmyren, Jmt</t>
+          <t>Slåtthornets kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495024.334450367</v>
+        <v>495321</v>
       </c>
       <c r="R13" t="n">
-        <v>6991924.280264216</v>
+        <v>6991909</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,22 +1881,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2010-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2010-08-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Borgsjöveckan 2010: Exk. obj. 145 A. Slåtthornets kalkbarrskog, norra delen,</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,63 +1906,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110156321</v>
+        <v>90840026</v>
       </c>
       <c r="B14" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lassmyren, Jmt</t>
+          <t>Slåtthornet-Lassmyren_S, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495066.5441764466</v>
+        <v>494921</v>
       </c>
       <c r="R14" t="n">
-        <v>6991907.889567481</v>
+        <v>6991696</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2174,22 +1987,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,6 +2003,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2209,22 +2017,21 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110156308</v>
+        <v>121495680</v>
       </c>
       <c r="B15" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,38 +2039,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>4405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lassmyren, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495024.334450367</v>
+        <v>495280</v>
       </c>
       <c r="R15" t="n">
-        <v>6991924.280264216</v>
+        <v>6992032</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,22 +2093,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2317,27 +2113,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110156471</v>
+        <v>121495630</v>
       </c>
       <c r="B16" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,42 +2136,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåtthornets naturreservat, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495223.3247358568</v>
+        <v>495282</v>
       </c>
       <c r="R16" t="n">
-        <v>6991977.948649338</v>
+        <v>6992024</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,22 +2190,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,27 +2210,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110156872</v>
+        <v>121495639</v>
       </c>
       <c r="B17" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,38 +2233,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåtthornets naturreservat, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495346.3684882029</v>
+        <v>495383</v>
       </c>
       <c r="R17" t="n">
-        <v>6991960.53702251</v>
+        <v>6991903</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2517,22 +2287,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,75 +2307,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110156092</v>
+        <v>121495691</v>
       </c>
       <c r="B18" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåtthornets naturreservat, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494987.7056718415</v>
+        <v>494951</v>
       </c>
       <c r="R18" t="n">
-        <v>6991731.136365773</v>
+        <v>6991725</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2639,22 +2384,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,67 +2404,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110156156</v>
+        <v>103955088</v>
       </c>
       <c r="B19" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>5747</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåtthornets naturreservat, Jmt</t>
+          <t>Slåttbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495013.1867452738</v>
+        <v>495311</v>
       </c>
       <c r="R19" t="n">
-        <v>6991762.390927578</v>
+        <v>6991959</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2756,22 +2484,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,69 +2498,67 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110155896</v>
+        <v>121342774</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåtthornets naturreservat, Jmt</t>
+          <t>Slåttbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495043.4402559365</v>
+        <v>495087</v>
       </c>
       <c r="R20" t="n">
-        <v>6991647.59936113</v>
+        <v>6991899</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2869,22 +2585,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,71 +2599,67 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>90840014</v>
+        <v>121495689</v>
       </c>
       <c r="B21" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>5747</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåtthornet-Lassmyren_N, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494974.8948032015</v>
+        <v>495313</v>
       </c>
       <c r="R21" t="n">
-        <v>6991963.811319271</v>
+        <v>6991964</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2981,22 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3007,81 +2699,64 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121342793</v>
+        <v>121495699</v>
       </c>
       <c r="B22" t="n">
-        <v>91998</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttbodarna, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495144</v>
+        <v>495037</v>
       </c>
       <c r="R22" t="n">
-        <v>6991986</v>
+        <v>6991941</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3105,12 +2780,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,34 +2794,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121342774</v>
+        <v>121495715</v>
       </c>
       <c r="B23" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,26 +2837,23 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttbodarna, Jmt</t>
+          <t>Slåtthornet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495087</v>
+        <v>495040</v>
       </c>
       <c r="R23" t="n">
-        <v>6991899</v>
+        <v>6991932</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3211,12 +2877,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,34 +2891,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Amanda Evensen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121495705</v>
+        <v>62064693</v>
       </c>
       <c r="B24" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,34 +2920,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornets kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495117</v>
+        <v>495349</v>
       </c>
       <c r="R24" t="n">
-        <v>6991892</v>
+        <v>6991899</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,12 +2974,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2010-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2010-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Borgsjöveckan 2010: Exk. obj. 145 A. Slåtthornets kalkbarrskog, norra delen,</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,49 +2999,48 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121495724</v>
+        <v>121495686</v>
       </c>
       <c r="B25" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495179</v>
+        <v>494949</v>
       </c>
       <c r="R25" t="n">
-        <v>6992005</v>
+        <v>6991727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,37 +3112,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121495710</v>
+        <v>121495695</v>
       </c>
       <c r="B26" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494983</v>
+        <v>495069</v>
       </c>
       <c r="R26" t="n">
-        <v>6991722</v>
+        <v>6991736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,37 +3209,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121495684</v>
+        <v>121495700</v>
       </c>
       <c r="B27" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3590,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495352</v>
+        <v>495333</v>
       </c>
       <c r="R27" t="n">
-        <v>6991979</v>
+        <v>6991958</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,37 +3306,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121495689</v>
+        <v>121495705</v>
       </c>
       <c r="B28" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3692,10 +3341,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495313</v>
+        <v>495117</v>
       </c>
       <c r="R28" t="n">
-        <v>6991964</v>
+        <v>6991892</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,37 +3403,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121495713</v>
+        <v>121495711</v>
       </c>
       <c r="B29" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,10 +3438,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494943</v>
+        <v>495151</v>
       </c>
       <c r="R29" t="n">
-        <v>6991755</v>
+        <v>6991946</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,37 +3500,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121495709</v>
+        <v>121495723</v>
       </c>
       <c r="B30" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3896,10 +3535,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495057</v>
+        <v>494964</v>
       </c>
       <c r="R30" t="n">
-        <v>6991872</v>
+        <v>6991779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,53 +3597,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121495697</v>
+        <v>110153231</v>
       </c>
       <c r="B31" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>100453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495040</v>
+        <v>494968</v>
       </c>
       <c r="R31" t="n">
-        <v>6991930</v>
+        <v>6991639</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4028,12 +3663,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,65 +3693,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121495706</v>
+        <v>110156841</v>
       </c>
       <c r="B32" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495276</v>
+        <v>495326</v>
       </c>
       <c r="R32" t="n">
-        <v>6991998</v>
+        <v>6991909</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4130,12 +3771,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,27 +3801,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121495716</v>
+        <v>110156092</v>
       </c>
       <c r="B33" t="n">
-        <v>92035</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,37 +3824,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1968</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495158</v>
+        <v>494988</v>
       </c>
       <c r="R33" t="n">
-        <v>6991970</v>
+        <v>6991731</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,12 +3888,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,27 +3918,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121495683</v>
+        <v>121495692</v>
       </c>
       <c r="B34" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,21 +3941,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +3965,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495158</v>
+        <v>495190</v>
       </c>
       <c r="R34" t="n">
-        <v>6991970</v>
+        <v>6991952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4366,15 +4027,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121495686</v>
+        <v>121495709</v>
       </c>
       <c r="B35" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,21 +4038,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4062,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494949</v>
+        <v>495057</v>
       </c>
       <c r="R35" t="n">
-        <v>6991727</v>
+        <v>6991872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4468,15 +4124,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121495726</v>
+        <v>91133104</v>
       </c>
       <c r="B36" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4484,37 +4135,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494938</v>
+        <v>495040</v>
       </c>
       <c r="R36" t="n">
-        <v>6991772</v>
+        <v>6991893</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4538,12 +4189,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4554,31 +4205,35 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121495715</v>
+        <v>121495704</v>
       </c>
       <c r="B37" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4586,21 +4241,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495040</v>
+        <v>495047</v>
       </c>
       <c r="R37" t="n">
-        <v>6991932</v>
+        <v>6991920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,37 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121495696</v>
+        <v>121495710</v>
       </c>
       <c r="B38" t="n">
-        <v>91998</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495158</v>
+        <v>494983</v>
       </c>
       <c r="R38" t="n">
-        <v>6991970</v>
+        <v>6991722</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4774,37 +4424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121495723</v>
+        <v>121495724</v>
       </c>
       <c r="B39" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494964</v>
+        <v>495179</v>
       </c>
       <c r="R39" t="n">
-        <v>6991779</v>
+        <v>6992005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4876,15 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121495654</v>
+        <v>121495722</v>
       </c>
       <c r="B40" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4892,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>221063</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495089</v>
+        <v>495023</v>
       </c>
       <c r="R40" t="n">
-        <v>6992087</v>
+        <v>6991790</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4946,12 +4586,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,53 +4618,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121495688</v>
+        <v>90840024</v>
       </c>
       <c r="B41" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornet-Lassmyren_N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495370</v>
+        <v>495093</v>
       </c>
       <c r="R41" t="n">
-        <v>6991950</v>
+        <v>6991890</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5048,12 +4683,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5064,69 +4699,73 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121495694</v>
+        <v>91133094</v>
       </c>
       <c r="B42" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495054</v>
+        <v>494974</v>
       </c>
       <c r="R42" t="n">
-        <v>6991738</v>
+        <v>6991681</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5150,12 +4789,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5166,69 +4805,74 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121495725</v>
+        <v>110156305</v>
       </c>
       <c r="B43" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Lassmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494962</v>
+        <v>495024</v>
       </c>
       <c r="R43" t="n">
-        <v>6991783</v>
+        <v>6991925</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5252,12 +4896,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5272,65 +4926,61 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121495695</v>
+        <v>110156321</v>
       </c>
       <c r="B44" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Lassmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495069</v>
+        <v>495067</v>
       </c>
       <c r="R44" t="n">
-        <v>6991736</v>
+        <v>6991908</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5354,12 +5004,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5374,65 +5034,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121495659</v>
+        <v>110156872</v>
       </c>
       <c r="B45" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494954</v>
+        <v>495347</v>
       </c>
       <c r="R45" t="n">
-        <v>6992160</v>
+        <v>6991960</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5456,12 +5112,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5476,49 +5142,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121495693</v>
+        <v>121495684</v>
       </c>
       <c r="B46" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5528,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495317</v>
+        <v>495352</v>
       </c>
       <c r="R46" t="n">
-        <v>6991944</v>
+        <v>6991979</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5590,37 +5251,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121495700</v>
+        <v>121495697</v>
       </c>
       <c r="B47" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5630,10 +5286,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495333</v>
+        <v>495040</v>
       </c>
       <c r="R47" t="n">
-        <v>6991958</v>
+        <v>6991930</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,37 +5348,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121495699</v>
+        <v>121495701</v>
       </c>
       <c r="B48" t="n">
-        <v>90262</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5732,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495037</v>
+        <v>495371</v>
       </c>
       <c r="R48" t="n">
-        <v>6991941</v>
+        <v>6991950</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,19 +5445,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121495701</v>
+        <v>121495713</v>
       </c>
       <c r="B49" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5834,10 +5480,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495371</v>
+        <v>494943</v>
       </c>
       <c r="R49" t="n">
-        <v>6991950</v>
+        <v>6991755</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,53 +5542,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121495746</v>
+        <v>90840023</v>
       </c>
       <c r="B50" t="n">
-        <v>90189</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3286</v>
+        <v>222412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Slåtthornet-Lassmyren_N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495314</v>
+        <v>495093</v>
       </c>
       <c r="R50" t="n">
-        <v>6991947</v>
+        <v>6991890</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5966,12 +5607,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5982,53 +5623,57 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121495704</v>
+        <v>121495682</v>
       </c>
       <c r="B51" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6038,10 +5683,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495047</v>
+        <v>495314</v>
       </c>
       <c r="R51" t="n">
-        <v>6991920</v>
+        <v>6991997</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,15 +5745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121495682</v>
+        <v>121495693</v>
       </c>
       <c r="B52" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6140,10 +5780,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495314</v>
+        <v>495317</v>
       </c>
       <c r="R52" t="n">
-        <v>6991997</v>
+        <v>6991944</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,15 +5842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121495712</v>
+        <v>121495694</v>
       </c>
       <c r="B53" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6218,16 +5853,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6242,10 +5877,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495313</v>
+        <v>495054</v>
       </c>
       <c r="R53" t="n">
-        <v>6991949</v>
+        <v>6991738</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,15 +5939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121495634</v>
+        <v>121495702</v>
       </c>
       <c r="B54" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6320,21 +5950,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6344,10 +5974,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495050</v>
+        <v>495369</v>
       </c>
       <c r="R54" t="n">
-        <v>6992120</v>
+        <v>6991950</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6374,12 +6004,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6406,15 +6036,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121495702</v>
+        <v>121495725</v>
       </c>
       <c r="B55" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,10 +6071,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495369</v>
+        <v>494962</v>
       </c>
       <c r="R55" t="n">
-        <v>6991950</v>
+        <v>6991783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6508,15 +6133,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121495691</v>
+        <v>121495726</v>
       </c>
       <c r="B56" t="n">
-        <v>91661</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6524,21 +6144,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6168,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494951</v>
+        <v>494938</v>
       </c>
       <c r="R56" t="n">
-        <v>6991725</v>
+        <v>6991772</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,15 +6230,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121495717</v>
+        <v>91133097</v>
       </c>
       <c r="B57" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6626,37 +6241,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495355</v>
+        <v>494974</v>
       </c>
       <c r="R57" t="n">
-        <v>6991976</v>
+        <v>6991681</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6680,12 +6295,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,31 +6311,35 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121495722</v>
+        <v>91133106</v>
       </c>
       <c r="B58" t="n">
-        <v>97126</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6728,37 +6347,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221063</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slåtthornet, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495023</v>
+        <v>495040</v>
       </c>
       <c r="R58" t="n">
-        <v>6991790</v>
+        <v>6991893</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6782,12 +6401,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,19 +6417,1128 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Amanda Evensen</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>110155896</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Slåtthornets naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>495043</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6991648</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>110156308</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lassmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>495024</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6991925</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121495634</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>495050</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6992120</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121495654</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>495089</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6992087</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121495659</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>494954</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6992160</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121495661</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>495383</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6991894</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121495688</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>495370</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6991950</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121495706</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>495276</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6991998</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>110156734</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Slåtthornets naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>495310</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6991906</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121495712</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>495313</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6991949</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121495717</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Slåtthornet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>495355</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6991976</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Amanda Evensen</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12943-2022 artfynd.xlsx
+++ b/artfynd/A 12943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840014</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156471</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62064305</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840027</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495683</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121342793</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495696</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90643329</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62064309</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495680</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495630</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495639</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495691</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2514,6 +2604,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103955088</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121342774</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495689</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495699</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495715</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62064693</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3109,6 +3229,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495686</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495695</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3303,6 +3433,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495700</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3400,6 +3535,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495705</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3497,6 +3637,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495711</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3594,6 +3739,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495723</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110153231</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3810,6 +3965,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156841</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3927,6 +4087,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156092</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4024,6 +4189,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495692</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4121,6 +4291,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495709</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4227,6 +4402,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133104</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495704</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4421,6 +4606,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495710</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4518,6 +4708,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495724</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4615,6 +4810,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495722</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4721,6 +4921,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840024</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4827,6 +5032,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133094</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4935,6 +5145,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156305</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5043,6 +5258,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156321</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5151,6 +5371,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156872</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5248,6 +5473,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495684</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5345,6 +5575,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495697</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5442,6 +5677,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495701</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5539,6 +5779,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495713</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5645,6 +5890,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840023</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5742,6 +5992,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495682</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5839,6 +6094,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495693</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5936,6 +6196,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495694</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6033,6 +6298,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495702</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6130,6 +6400,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495725</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6227,6 +6502,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495726</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6333,6 +6613,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133097</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6439,6 +6724,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133106</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6547,6 +6837,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110155896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6655,6 +6950,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156308</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6752,6 +7052,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495634</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6849,6 +7154,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495654</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6946,6 +7256,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495659</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7043,6 +7358,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495661</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7140,6 +7460,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495688</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7237,6 +7562,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495706</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7345,6 +7675,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110156734</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7442,6 +7777,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495712</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7539,8 +7879,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121495717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>